--- a/research/traditional_assets/database/data/isle_of_man/isle_of_man_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/isle_of_man/isle_of_man_electronics_general.xlsx
@@ -1133,43 +1133,43 @@
         <v>3.0077519379845</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>387.808545246894</v>
       </c>
       <c r="G2">
         <v>2.57634408602151</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0555913978494624</v>
       </c>
       <c r="I2">
         <v>0.463442940038685</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>138.7</v>
       </c>
       <c r="L2">
-        <v>270.343862428851</v>
+        <v>267.680605085327</v>
       </c>
       <c r="M2">
         <v>233.3</v>
       </c>
       <c r="N2">
-        <v>245.143862428851</v>
+        <v>245.065605085327</v>
       </c>
       <c r="O2">
         <v>119.8</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.585</v>
       </c>
       <c r="Q2">
         <v>0.118450748630295</v>
       </c>
       <c r="R2">
-        <v>0.11129675761996</v>
+        <v>0.11134175761996</v>
       </c>
       <c r="S2">
         <v>0.0612366166625341</v>
@@ -1191,13 +1191,13 @@
         <v>0.167868578549097</v>
       </c>
       <c r="X2">
-        <v>0.11129675761996</v>
+        <v>0.111958341030263</v>
       </c>
       <c r="Y2">
         <v>2.37934380204767</v>
       </c>
       <c r="Z2">
-        <v>1.27665371506388</v>
+        <v>1.28954920713523</v>
       </c>
       <c r="AA2">
         <v>119.8</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1112967576199604</v>
+        <v>0.1113417576199604</v>
       </c>
       <c r="C2">
-        <v>270.3438624288512</v>
+        <v>267.6806050853273</v>
       </c>
       <c r="D2">
-        <v>245.1438624288512</v>
+        <v>245.0656050853272</v>
       </c>
       <c r="E2">
-        <v>-119.8</v>
+        <v>-117.215</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.585</v>
       </c>
       <c r="G2">
         <v>25.2</v>
@@ -1451,28 +1451,28 @@
         <v>50.425</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1300255</v>
       </c>
       <c r="N2">
-        <v>50.425</v>
+        <v>50.2949745</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>50.425</v>
+        <v>50.2949745</v>
       </c>
       <c r="Q2">
-        <v>58.125</v>
+        <v>57.9949745</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1112967576199604</v>
+        <v>0.111958341030263</v>
       </c>
       <c r="T2">
-        <v>1.276653715063877</v>
+        <v>1.28954920713523</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>387.8085452468939</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1113417576199604</v>
+        <v>0.1113867576199604</v>
       </c>
       <c r="C3">
-        <v>267.6806050853273</v>
+        <v>265.0173976900854</v>
       </c>
       <c r="D3">
-        <v>245.0656050853272</v>
+        <v>244.9873976900855</v>
       </c>
       <c r="E3">
-        <v>-117.215</v>
+        <v>-114.63</v>
       </c>
       <c r="F3">
-        <v>2.585</v>
+        <v>5.17</v>
       </c>
       <c r="G3">
         <v>25.2</v>
@@ -1533,28 +1533,28 @@
         <v>50.425</v>
       </c>
       <c r="M3">
-        <v>0.1300255</v>
+        <v>0.260051</v>
       </c>
       <c r="N3">
-        <v>50.2949745</v>
+        <v>50.164949</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>50.2949745</v>
+        <v>50.164949</v>
       </c>
       <c r="Q3">
-        <v>57.9949745</v>
+        <v>57.864949</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.111958341030263</v>
+        <v>0.1126334261428167</v>
       </c>
       <c r="T3">
-        <v>1.28954920713523</v>
+        <v>1.302707872514161</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>387.8085452468939</v>
+        <v>193.904272623447</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1113867576199604</v>
+        <v>0.1114317576199604</v>
       </c>
       <c r="C4">
-        <v>265.0173976900854</v>
+        <v>262.3542401953214</v>
       </c>
       <c r="D4">
-        <v>244.9873976900855</v>
+        <v>244.9092401953214</v>
       </c>
       <c r="E4">
-        <v>-114.63</v>
+        <v>-112.045</v>
       </c>
       <c r="F4">
-        <v>5.17</v>
+        <v>7.755</v>
       </c>
       <c r="G4">
         <v>25.2</v>
@@ -1615,28 +1615,28 @@
         <v>50.425</v>
       </c>
       <c r="M4">
-        <v>0.260051</v>
+        <v>0.3900765</v>
       </c>
       <c r="N4">
-        <v>50.164949</v>
+        <v>50.0349235</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>50.164949</v>
+        <v>50.0349235</v>
       </c>
       <c r="Q4">
-        <v>57.864949</v>
+        <v>57.7349235</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1126334261428167</v>
+        <v>0.1133224305360416</v>
       </c>
       <c r="T4">
-        <v>1.302707872514161</v>
+        <v>1.316137850581317</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>193.904272623447</v>
+        <v>129.2695150822979</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1114317576199604</v>
+        <v>0.1114767576199604</v>
       </c>
       <c r="C5">
-        <v>262.3542401953214</v>
+        <v>259.6911325532914</v>
       </c>
       <c r="D5">
-        <v>244.9092401953214</v>
+        <v>244.8311325532914</v>
       </c>
       <c r="E5">
-        <v>-112.045</v>
+        <v>-109.46</v>
       </c>
       <c r="F5">
-        <v>7.755</v>
+        <v>10.34</v>
       </c>
       <c r="G5">
         <v>25.2</v>
@@ -1697,28 +1697,28 @@
         <v>50.425</v>
       </c>
       <c r="M5">
-        <v>0.3900765</v>
+        <v>0.520102</v>
       </c>
       <c r="N5">
-        <v>50.0349235</v>
+        <v>49.904898</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>50.0349235</v>
+        <v>49.904898</v>
       </c>
       <c r="Q5">
-        <v>57.7349235</v>
+        <v>57.604898</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1133224305360416</v>
+        <v>0.1140257891874587</v>
       </c>
       <c r="T5">
-        <v>1.316137850581317</v>
+        <v>1.329847619858206</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>129.2695150822979</v>
+        <v>96.95213631172346</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1114767576199604</v>
+        <v>0.1115217576199604</v>
       </c>
       <c r="C6">
-        <v>259.6911325532914</v>
+        <v>257.0280747163129</v>
       </c>
       <c r="D6">
-        <v>244.8311325532914</v>
+        <v>244.7530747163129</v>
       </c>
       <c r="E6">
-        <v>-109.46</v>
+        <v>-106.875</v>
       </c>
       <c r="F6">
-        <v>10.34</v>
+        <v>12.925</v>
       </c>
       <c r="G6">
         <v>25.2</v>
@@ -1779,28 +1779,28 @@
         <v>50.425</v>
       </c>
       <c r="M6">
-        <v>0.520102</v>
+        <v>0.6501275</v>
       </c>
       <c r="N6">
-        <v>49.904898</v>
+        <v>49.7748725</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>49.904898</v>
+        <v>49.7748725</v>
       </c>
       <c r="Q6">
-        <v>57.604898</v>
+        <v>57.4748725</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1140257891874587</v>
+        <v>0.114743955389432</v>
       </c>
       <c r="T6">
-        <v>1.329847619858206</v>
+        <v>1.343846015856713</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>96.95213631172346</v>
+        <v>77.56170904937878</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1115217576199604</v>
+        <v>0.1115667576199604</v>
       </c>
       <c r="C7">
-        <v>257.0280747163129</v>
+        <v>254.3650666367643</v>
       </c>
       <c r="D7">
-        <v>244.7530747163129</v>
+        <v>244.6750666367643</v>
       </c>
       <c r="E7">
-        <v>-106.875</v>
+        <v>-104.29</v>
       </c>
       <c r="F7">
-        <v>12.925</v>
+        <v>15.51</v>
       </c>
       <c r="G7">
         <v>25.2</v>
@@ -1861,28 +1861,28 @@
         <v>50.425</v>
       </c>
       <c r="M7">
-        <v>0.6501275</v>
+        <v>0.780153</v>
       </c>
       <c r="N7">
-        <v>49.7748725</v>
+        <v>49.644847</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>49.7748725</v>
+        <v>49.644847</v>
       </c>
       <c r="Q7">
-        <v>57.4748725</v>
+        <v>57.344847</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.114743955389432</v>
+        <v>0.1154774017233621</v>
       </c>
       <c r="T7">
-        <v>1.343846015856713</v>
+        <v>1.358142250067955</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>77.56170904937878</v>
+        <v>64.63475754114899</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1115667576199604</v>
+        <v>0.1116117576199604</v>
       </c>
       <c r="C8">
-        <v>254.3650666367643</v>
+        <v>251.7021082670842</v>
       </c>
       <c r="D8">
-        <v>244.6750666367643</v>
+        <v>244.5971082670842</v>
       </c>
       <c r="E8">
-        <v>-104.29</v>
+        <v>-101.705</v>
       </c>
       <c r="F8">
-        <v>15.51</v>
+        <v>18.095</v>
       </c>
       <c r="G8">
         <v>25.2</v>
@@ -1943,28 +1943,28 @@
         <v>50.425</v>
       </c>
       <c r="M8">
-        <v>0.780153</v>
+        <v>0.9101784999999999</v>
       </c>
       <c r="N8">
-        <v>49.644847</v>
+        <v>49.5148215</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>49.644847</v>
+        <v>49.5148215</v>
       </c>
       <c r="Q8">
-        <v>57.344847</v>
+        <v>57.2148215</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1154774017233621</v>
+        <v>0.1162266210967316</v>
       </c>
       <c r="T8">
-        <v>1.358142250067955</v>
+        <v>1.372745930176212</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>64.63475754114899</v>
+        <v>55.40122074955627</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1116117576199604</v>
+        <v>0.1116567576199604</v>
       </c>
       <c r="C9">
-        <v>251.7021082670842</v>
+        <v>249.039199559772</v>
       </c>
       <c r="D9">
-        <v>244.5971082670842</v>
+        <v>244.5191995597721</v>
       </c>
       <c r="E9">
-        <v>-101.705</v>
+        <v>-99.12</v>
       </c>
       <c r="F9">
-        <v>18.095</v>
+        <v>20.68</v>
       </c>
       <c r="G9">
         <v>25.2</v>
@@ -2025,28 +2025,28 @@
         <v>50.425</v>
       </c>
       <c r="M9">
-        <v>0.9101785000000001</v>
+        <v>1.040204</v>
       </c>
       <c r="N9">
-        <v>49.5148215</v>
+        <v>49.38479599999999</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>49.5148215</v>
+        <v>49.38479599999999</v>
       </c>
       <c r="Q9">
-        <v>57.2148215</v>
+        <v>57.084796</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1162266210967316</v>
+        <v>0.116992127847783</v>
       </c>
       <c r="T9">
-        <v>1.372745930176212</v>
+        <v>1.387667081591171</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>55.40122074955626</v>
+        <v>48.47606815586173</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1116567576199604</v>
+        <v>0.1117017576199604</v>
       </c>
       <c r="C10">
-        <v>249.039199559772</v>
+        <v>246.376340467388</v>
       </c>
       <c r="D10">
-        <v>244.5191995597721</v>
+        <v>244.441340467388</v>
       </c>
       <c r="E10">
-        <v>-99.12</v>
+        <v>-96.535</v>
       </c>
       <c r="F10">
-        <v>20.68</v>
+        <v>23.265</v>
       </c>
       <c r="G10">
         <v>25.2</v>
@@ -2107,28 +2107,28 @@
         <v>50.425</v>
       </c>
       <c r="M10">
-        <v>1.040204</v>
+        <v>1.1702295</v>
       </c>
       <c r="N10">
-        <v>49.38479599999999</v>
+        <v>49.2547705</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>49.38479599999999</v>
+        <v>49.2547705</v>
       </c>
       <c r="Q10">
-        <v>57.084796</v>
+        <v>56.9547705</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.116992127847783</v>
+        <v>0.1177744589230334</v>
       </c>
       <c r="T10">
-        <v>1.387667081591171</v>
+        <v>1.402916170399865</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>48.47606815586173</v>
+        <v>43.08983836076599</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1117017576199604</v>
+        <v>0.1117467576199604</v>
       </c>
       <c r="C11">
-        <v>246.376340467388</v>
+        <v>243.7135309425522</v>
       </c>
       <c r="D11">
-        <v>244.441340467388</v>
+        <v>244.3635309425522</v>
       </c>
       <c r="E11">
-        <v>-96.535</v>
+        <v>-93.95</v>
       </c>
       <c r="F11">
-        <v>23.265</v>
+        <v>25.85</v>
       </c>
       <c r="G11">
         <v>25.2</v>
@@ -2189,28 +2189,28 @@
         <v>50.425</v>
       </c>
       <c r="M11">
-        <v>1.1702295</v>
+        <v>1.300255</v>
       </c>
       <c r="N11">
-        <v>49.2547705</v>
+        <v>49.124745</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>49.2547705</v>
+        <v>49.124745</v>
       </c>
       <c r="Q11">
-        <v>56.9547705</v>
+        <v>56.824745</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1177744589230334</v>
+        <v>0.1185741751332893</v>
       </c>
       <c r="T11">
-        <v>1.402916170399865</v>
+        <v>1.418504127848753</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>43.08983836076599</v>
+        <v>38.78085452468939</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1117467576199604</v>
+        <v>0.1117917576199604</v>
       </c>
       <c r="C12">
-        <v>243.7135309425522</v>
+        <v>241.0507709379456</v>
       </c>
       <c r="D12">
-        <v>244.3635309425522</v>
+        <v>244.2857709379456</v>
       </c>
       <c r="E12">
-        <v>-93.94999999999999</v>
+        <v>-91.36499999999999</v>
       </c>
       <c r="F12">
-        <v>25.85</v>
+        <v>28.435</v>
       </c>
       <c r="G12">
         <v>25.2</v>
@@ -2271,28 +2271,28 @@
         <v>50.425</v>
       </c>
       <c r="M12">
-        <v>1.300255</v>
+        <v>1.4302805</v>
       </c>
       <c r="N12">
-        <v>49.124745</v>
+        <v>48.9947195</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>49.124745</v>
+        <v>48.9947195</v>
       </c>
       <c r="Q12">
-        <v>56.824745</v>
+        <v>56.6947195</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1185741751332893</v>
+        <v>0.1193918624943375</v>
       </c>
       <c r="T12">
-        <v>1.418504127848753</v>
+        <v>1.434442376476267</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>38.78085452468939</v>
+        <v>35.25532229517217</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1117917576199604</v>
+        <v>0.1118367576199604</v>
       </c>
       <c r="C13">
-        <v>241.0507709379456</v>
+        <v>238.3880604063087</v>
       </c>
       <c r="D13">
-        <v>244.2857709379456</v>
+        <v>244.2080604063087</v>
       </c>
       <c r="E13">
-        <v>-91.36499999999999</v>
+        <v>-88.78</v>
       </c>
       <c r="F13">
-        <v>28.435</v>
+        <v>31.02</v>
       </c>
       <c r="G13">
         <v>25.2</v>
@@ -2353,28 +2353,28 @@
         <v>50.425</v>
       </c>
       <c r="M13">
-        <v>1.4302805</v>
+        <v>1.560306</v>
       </c>
       <c r="N13">
-        <v>48.9947195</v>
+        <v>48.864694</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>48.9947195</v>
+        <v>48.864694</v>
       </c>
       <c r="Q13">
-        <v>56.6947195</v>
+        <v>56.564694</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1193918624943375</v>
+        <v>0.1202281336590459</v>
       </c>
       <c r="T13">
-        <v>1.434442376476267</v>
+        <v>1.450742858027133</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>35.25532229517217</v>
+        <v>32.31737877057449</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1118367576199604</v>
+        <v>0.1118817576199604</v>
       </c>
       <c r="C14">
-        <v>238.3880604063087</v>
+        <v>235.7253993004429</v>
       </c>
       <c r="D14">
-        <v>244.2080604063087</v>
+        <v>244.1303993004429</v>
       </c>
       <c r="E14">
-        <v>-88.78</v>
+        <v>-86.19499999999999</v>
       </c>
       <c r="F14">
-        <v>31.02</v>
+        <v>33.605</v>
       </c>
       <c r="G14">
         <v>25.2</v>
@@ -2435,28 +2435,28 @@
         <v>50.425</v>
       </c>
       <c r="M14">
-        <v>1.560306</v>
+        <v>1.6903315</v>
       </c>
       <c r="N14">
-        <v>48.864694</v>
+        <v>48.7346685</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>48.864694</v>
+        <v>48.7346685</v>
       </c>
       <c r="Q14">
-        <v>56.564694</v>
+        <v>56.4346685</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1202281336590459</v>
+        <v>0.1210836294482303</v>
       </c>
       <c r="T14">
-        <v>1.450742858027133</v>
+        <v>1.467418063291813</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>32.31737877057449</v>
+        <v>29.83142655745337</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1118817576199604</v>
+        <v>0.1119267576199604</v>
       </c>
       <c r="C15">
-        <v>235.7253993004429</v>
+        <v>233.062787573209</v>
       </c>
       <c r="D15">
-        <v>244.1303993004429</v>
+        <v>244.052787573209</v>
       </c>
       <c r="E15">
-        <v>-86.19499999999999</v>
+        <v>-83.60999999999999</v>
       </c>
       <c r="F15">
-        <v>33.605</v>
+        <v>36.19</v>
       </c>
       <c r="G15">
         <v>25.2</v>
@@ -2517,28 +2517,28 @@
         <v>50.425</v>
       </c>
       <c r="M15">
-        <v>1.6903315</v>
+        <v>1.820357</v>
       </c>
       <c r="N15">
-        <v>48.7346685</v>
+        <v>48.604643</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>48.7346685</v>
+        <v>48.604643</v>
       </c>
       <c r="Q15">
-        <v>56.4346685</v>
+        <v>56.304643</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1210836294482303</v>
+        <v>0.121959020488326</v>
       </c>
       <c r="T15">
-        <v>1.467418063291813</v>
+        <v>1.484481064027764</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>29.83142655745337</v>
+        <v>27.70061037477813</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1119267576199604</v>
+        <v>0.1119717576199604</v>
       </c>
       <c r="C16">
-        <v>233.062787573209</v>
+        <v>230.4002251775279</v>
       </c>
       <c r="D16">
-        <v>244.052787573209</v>
+        <v>243.9752251775279</v>
       </c>
       <c r="E16">
-        <v>-83.60999999999999</v>
+        <v>-81.02499999999999</v>
       </c>
       <c r="F16">
-        <v>36.19</v>
+        <v>38.77500000000001</v>
       </c>
       <c r="G16">
         <v>25.2</v>
@@ -2599,28 +2599,28 @@
         <v>50.425</v>
       </c>
       <c r="M16">
-        <v>1.820357</v>
+        <v>1.9503825</v>
       </c>
       <c r="N16">
-        <v>48.604643</v>
+        <v>48.47461749999999</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>48.604643</v>
+        <v>48.47461749999999</v>
       </c>
       <c r="Q16">
-        <v>56.304643</v>
+        <v>56.1746175</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.121959020488326</v>
+        <v>0.1228550089646593</v>
       </c>
       <c r="T16">
-        <v>1.484481064027764</v>
+        <v>1.501945547133973</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>27.70061037477813</v>
+        <v>25.85390301645959</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1119717576199604</v>
+        <v>0.1120167576199604</v>
       </c>
       <c r="C17">
-        <v>230.4002251775279</v>
+        <v>227.7377120663805</v>
       </c>
       <c r="D17">
-        <v>243.9752251775279</v>
+        <v>243.8977120663805</v>
       </c>
       <c r="E17">
-        <v>-81.02500000000001</v>
+        <v>-78.44</v>
       </c>
       <c r="F17">
-        <v>38.775</v>
+        <v>41.36</v>
       </c>
       <c r="G17">
         <v>25.2</v>
@@ -2681,28 +2681,28 @@
         <v>50.425</v>
       </c>
       <c r="M17">
-        <v>1.9503825</v>
+        <v>2.080408</v>
       </c>
       <c r="N17">
-        <v>48.47461749999999</v>
+        <v>48.344592</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>48.47461749999999</v>
+        <v>48.344592</v>
       </c>
       <c r="Q17">
-        <v>56.1746175</v>
+        <v>56.044592</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1228550089646593</v>
+        <v>0.1237723304999528</v>
       </c>
       <c r="T17">
-        <v>1.501945547133973</v>
+        <v>1.519825851266521</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>25.85390301645959</v>
+        <v>24.23803407793087</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1120167576199604</v>
+        <v>0.1120617576199604</v>
       </c>
       <c r="C18">
-        <v>227.7377120663805</v>
+        <v>225.0752481928072</v>
       </c>
       <c r="D18">
-        <v>243.8977120663805</v>
+        <v>243.8202481928072</v>
       </c>
       <c r="E18">
-        <v>-78.44</v>
+        <v>-75.85499999999999</v>
       </c>
       <c r="F18">
-        <v>41.36</v>
+        <v>43.945</v>
       </c>
       <c r="G18">
         <v>25.2</v>
@@ -2763,28 +2763,28 @@
         <v>50.425</v>
       </c>
       <c r="M18">
-        <v>2.080408</v>
+        <v>2.2104335</v>
       </c>
       <c r="N18">
-        <v>48.344592</v>
+        <v>48.2145665</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>48.344592</v>
+        <v>48.2145665</v>
       </c>
       <c r="Q18">
-        <v>56.044592</v>
+        <v>55.9145665</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1237723304999528</v>
+        <v>0.124711756168627</v>
       </c>
       <c r="T18">
-        <v>1.519825851266521</v>
+        <v>1.538137006101057</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>24.23803407793087</v>
+        <v>22.81226736746435</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1120617576199604</v>
+        <v>0.1121067576199604</v>
       </c>
       <c r="C19">
-        <v>225.0752481928072</v>
+        <v>222.4128335099083</v>
       </c>
       <c r="D19">
-        <v>243.8202481928072</v>
+        <v>243.7428335099083</v>
       </c>
       <c r="E19">
-        <v>-75.85499999999999</v>
+        <v>-73.26999999999998</v>
       </c>
       <c r="F19">
-        <v>43.945</v>
+        <v>46.53000000000001</v>
       </c>
       <c r="G19">
         <v>25.2</v>
@@ -2845,28 +2845,28 @@
         <v>50.425</v>
       </c>
       <c r="M19">
-        <v>2.2104335</v>
+        <v>2.340459000000001</v>
       </c>
       <c r="N19">
-        <v>48.2145665</v>
+        <v>48.08454099999999</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>48.2145665</v>
+        <v>48.08454099999999</v>
       </c>
       <c r="Q19">
-        <v>55.9145665</v>
+        <v>55.784541</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.124711756168627</v>
+        <v>0.1256740946584883</v>
       </c>
       <c r="T19">
-        <v>1.538137006101057</v>
+        <v>1.556894774468143</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>22.81226736746435</v>
+        <v>21.54491918038299</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1121067576199604</v>
+        <v>0.1121517576199604</v>
       </c>
       <c r="C20">
-        <v>222.4128335099083</v>
+        <v>219.7504679708433</v>
       </c>
       <c r="D20">
-        <v>243.7428335099083</v>
+        <v>243.6654679708433</v>
       </c>
       <c r="E20">
-        <v>-73.27</v>
+        <v>-70.685</v>
       </c>
       <c r="F20">
-        <v>46.53</v>
+        <v>49.115</v>
       </c>
       <c r="G20">
         <v>25.2</v>
@@ -2927,28 +2927,28 @@
         <v>50.425</v>
       </c>
       <c r="M20">
-        <v>2.340459</v>
+        <v>2.4704845</v>
       </c>
       <c r="N20">
-        <v>48.08454099999999</v>
+        <v>47.9545155</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>48.08454099999999</v>
+        <v>47.9545155</v>
       </c>
       <c r="Q20">
-        <v>55.784541</v>
+        <v>55.6545155</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1256740946584883</v>
+        <v>0.1266601945925437</v>
       </c>
       <c r="T20">
-        <v>1.556894774468143</v>
+        <v>1.576115697609725</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>21.54491918038299</v>
+        <v>20.410976065626</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1121517576199604</v>
+        <v>0.1121967576199604</v>
       </c>
       <c r="C21">
-        <v>219.7504679708433</v>
+        <v>217.0881515288315</v>
       </c>
       <c r="D21">
-        <v>243.6654679708433</v>
+        <v>243.5881515288315</v>
       </c>
       <c r="E21">
-        <v>-70.685</v>
+        <v>-68.09999999999999</v>
       </c>
       <c r="F21">
-        <v>49.115</v>
+        <v>51.7</v>
       </c>
       <c r="G21">
         <v>25.2</v>
@@ -3009,28 +3009,28 @@
         <v>50.425</v>
       </c>
       <c r="M21">
-        <v>2.4704845</v>
+        <v>2.60051</v>
       </c>
       <c r="N21">
-        <v>47.9545155</v>
+        <v>47.82449</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>47.9545155</v>
+        <v>47.82449</v>
       </c>
       <c r="Q21">
-        <v>55.6545155</v>
+        <v>55.52449</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1266601945925437</v>
+        <v>0.1276709470249505</v>
       </c>
       <c r="T21">
-        <v>1.576115697609725</v>
+        <v>1.595817143829847</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>20.410976065626</v>
+        <v>19.39042726234469</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1121967576199604</v>
+        <v>0.1122417576199604</v>
       </c>
       <c r="C22">
-        <v>217.0881515288315</v>
+        <v>214.4258841371514</v>
       </c>
       <c r="D22">
-        <v>243.5881515288315</v>
+        <v>243.5108841371514</v>
       </c>
       <c r="E22">
-        <v>-68.09999999999999</v>
+        <v>-65.51499999999999</v>
       </c>
       <c r="F22">
-        <v>51.7</v>
+        <v>54.285</v>
       </c>
       <c r="G22">
         <v>25.2</v>
@@ -3091,28 +3091,28 @@
         <v>50.425</v>
       </c>
       <c r="M22">
-        <v>2.60051</v>
+        <v>2.7305355</v>
       </c>
       <c r="N22">
-        <v>47.82449</v>
+        <v>47.6944645</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>47.82449</v>
+        <v>47.6944645</v>
       </c>
       <c r="Q22">
-        <v>55.52449</v>
+        <v>55.3944645</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1276709470249505</v>
+        <v>0.1287072881265321</v>
       </c>
       <c r="T22">
-        <v>1.595817143829847</v>
+        <v>1.616017360840351</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>19.39042726234469</v>
+        <v>18.46707358318542</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1122417576199604</v>
+        <v>0.1122867576199604</v>
       </c>
       <c r="C23">
-        <v>214.4258841371514</v>
+        <v>211.7636657491406</v>
       </c>
       <c r="D23">
-        <v>243.5108841371514</v>
+        <v>243.4336657491406</v>
       </c>
       <c r="E23">
-        <v>-65.515</v>
+        <v>-62.93</v>
       </c>
       <c r="F23">
-        <v>54.285</v>
+        <v>56.87</v>
       </c>
       <c r="G23">
         <v>25.2</v>
@@ -3173,28 +3173,28 @@
         <v>50.425</v>
       </c>
       <c r="M23">
-        <v>2.7305355</v>
+        <v>2.860561</v>
       </c>
       <c r="N23">
-        <v>47.6944645</v>
+        <v>47.564439</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>47.6944645</v>
+        <v>47.564439</v>
       </c>
       <c r="Q23">
-        <v>55.3944645</v>
+        <v>55.264439</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1287072881265321</v>
+        <v>0.1297702020768723</v>
       </c>
       <c r="T23">
-        <v>1.616017360840351</v>
+        <v>1.636735532133176</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>18.46707358318542</v>
+        <v>17.62766114758609</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1122867576199604</v>
+        <v>0.1123317576199604</v>
       </c>
       <c r="C24">
-        <v>211.7636657491406</v>
+        <v>209.1014963181961</v>
       </c>
       <c r="D24">
-        <v>243.4336657491406</v>
+        <v>243.3564963181962</v>
       </c>
       <c r="E24">
-        <v>-62.93</v>
+        <v>-60.34499999999999</v>
       </c>
       <c r="F24">
-        <v>56.87</v>
+        <v>59.45500000000001</v>
       </c>
       <c r="G24">
         <v>25.2</v>
@@ -3255,28 +3255,28 @@
         <v>50.425</v>
       </c>
       <c r="M24">
-        <v>2.860561</v>
+        <v>2.9905865</v>
       </c>
       <c r="N24">
-        <v>47.564439</v>
+        <v>47.4344135</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>47.564439</v>
+        <v>47.4344135</v>
       </c>
       <c r="Q24">
-        <v>55.264439</v>
+        <v>55.1344135</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1297702020768723</v>
+        <v>0.1308607241817667</v>
       </c>
       <c r="T24">
-        <v>1.636735532133176</v>
+        <v>1.657991837745295</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>17.62766114758609</v>
+        <v>16.86124109769104</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1123317576199604</v>
+        <v>0.1123767576199604</v>
       </c>
       <c r="C25">
-        <v>209.1014963181961</v>
+        <v>206.4393757977741</v>
       </c>
       <c r="D25">
-        <v>243.3564963181962</v>
+        <v>243.2793757977741</v>
       </c>
       <c r="E25">
-        <v>-60.34499999999999</v>
+        <v>-57.75999999999999</v>
       </c>
       <c r="F25">
-        <v>59.45500000000001</v>
+        <v>62.04000000000001</v>
       </c>
       <c r="G25">
         <v>25.2</v>
@@ -3337,28 +3337,28 @@
         <v>50.425</v>
       </c>
       <c r="M25">
-        <v>2.9905865</v>
+        <v>3.120612</v>
       </c>
       <c r="N25">
-        <v>47.4344135</v>
+        <v>47.304388</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>47.4344135</v>
+        <v>47.304388</v>
       </c>
       <c r="Q25">
-        <v>55.1344135</v>
+        <v>55.004388</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1308607241817667</v>
+        <v>0.13197994423679</v>
       </c>
       <c r="T25">
-        <v>1.657991837745295</v>
+        <v>1.679807519820891</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>16.86124109769104</v>
+        <v>16.15868938528725</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1123767576199604</v>
+        <v>0.1124217576199604</v>
       </c>
       <c r="C26">
-        <v>206.4393757977741</v>
+        <v>203.7773041413893</v>
       </c>
       <c r="D26">
-        <v>243.2793757977741</v>
+        <v>243.2023041413893</v>
       </c>
       <c r="E26">
-        <v>-57.76</v>
+        <v>-55.175</v>
       </c>
       <c r="F26">
-        <v>62.04</v>
+        <v>64.625</v>
       </c>
       <c r="G26">
         <v>25.2</v>
@@ -3419,28 +3419,28 @@
         <v>50.425</v>
       </c>
       <c r="M26">
-        <v>3.120612</v>
+        <v>3.2506375</v>
       </c>
       <c r="N26">
-        <v>47.304388</v>
+        <v>47.1743625</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>47.304388</v>
+        <v>47.1743625</v>
       </c>
       <c r="Q26">
-        <v>55.004388</v>
+        <v>54.8743625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.13197994423679</v>
+        <v>0.1331290101599472</v>
       </c>
       <c r="T26">
-        <v>1.679807519820891</v>
+        <v>1.702204953418503</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>16.15868938528725</v>
+        <v>15.51234180987576</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1124217576199604</v>
+        <v>0.1124667576199604</v>
       </c>
       <c r="C27">
-        <v>203.7773041413893</v>
+        <v>201.1152813026158</v>
       </c>
       <c r="D27">
-        <v>243.2023041413893</v>
+        <v>243.1252813026158</v>
       </c>
       <c r="E27">
-        <v>-55.175</v>
+        <v>-52.58999999999999</v>
       </c>
       <c r="F27">
-        <v>64.625</v>
+        <v>67.21000000000001</v>
       </c>
       <c r="G27">
         <v>25.2</v>
@@ -3501,28 +3501,28 @@
         <v>50.425</v>
       </c>
       <c r="M27">
-        <v>3.2506375</v>
+        <v>3.380663</v>
       </c>
       <c r="N27">
-        <v>47.1743625</v>
+        <v>47.044337</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>47.1743625</v>
+        <v>47.044337</v>
       </c>
       <c r="Q27">
-        <v>54.8743625</v>
+        <v>54.744337</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1331290101599472</v>
+        <v>0.1343091319188654</v>
       </c>
       <c r="T27">
-        <v>1.702204953418503</v>
+        <v>1.725207723059293</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>15.51234180987576</v>
+        <v>14.91571327872669</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1124667576199604</v>
+        <v>0.1125117576199604</v>
       </c>
       <c r="C28">
-        <v>201.1152813026158</v>
+        <v>198.4533072350861</v>
       </c>
       <c r="D28">
-        <v>243.1252813026158</v>
+        <v>243.0483072350861</v>
       </c>
       <c r="E28">
-        <v>-52.58999999999999</v>
+        <v>-50.005</v>
       </c>
       <c r="F28">
-        <v>67.21000000000001</v>
+        <v>69.795</v>
       </c>
       <c r="G28">
         <v>25.2</v>
@@ -3583,28 +3583,28 @@
         <v>50.425</v>
       </c>
       <c r="M28">
-        <v>3.380663</v>
+        <v>3.5106885</v>
       </c>
       <c r="N28">
-        <v>47.044337</v>
+        <v>46.9143115</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>47.044337</v>
+        <v>46.9143115</v>
       </c>
       <c r="Q28">
-        <v>54.744337</v>
+        <v>54.6143115</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1343091319188654</v>
+        <v>0.1355215857807676</v>
       </c>
       <c r="T28">
-        <v>1.725207723059293</v>
+        <v>1.748840705566955</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>14.91571327872669</v>
+        <v>14.36327945358866</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1125117576199604</v>
+        <v>0.1125567576199604</v>
       </c>
       <c r="C29">
-        <v>198.4533072350861</v>
+        <v>195.7913818924917</v>
       </c>
       <c r="D29">
-        <v>243.0483072350861</v>
+        <v>242.9713818924917</v>
       </c>
       <c r="E29">
-        <v>-50.005</v>
+        <v>-47.41999999999999</v>
       </c>
       <c r="F29">
-        <v>69.795</v>
+        <v>72.38000000000001</v>
       </c>
       <c r="G29">
         <v>25.2</v>
@@ -3665,28 +3665,28 @@
         <v>50.425</v>
       </c>
       <c r="M29">
-        <v>3.5106885</v>
+        <v>3.640714</v>
       </c>
       <c r="N29">
-        <v>46.9143115</v>
+        <v>46.78428599999999</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>46.9143115</v>
+        <v>46.78428599999999</v>
       </c>
       <c r="Q29">
-        <v>54.6143115</v>
+        <v>54.484286</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1355215857807676</v>
+        <v>0.1367677189166116</v>
       </c>
       <c r="T29">
-        <v>1.748840705566955</v>
+        <v>1.773130159810941</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.36327945358866</v>
+        <v>13.85030518738906</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1125567576199604</v>
+        <v>0.1126017576199604</v>
       </c>
       <c r="C30">
-        <v>195.7913818924917</v>
+        <v>193.1295052285825</v>
       </c>
       <c r="D30">
-        <v>242.9713818924917</v>
+        <v>242.8945052285825</v>
       </c>
       <c r="E30">
-        <v>-47.41999999999999</v>
+        <v>-44.83499999999999</v>
       </c>
       <c r="F30">
-        <v>72.38000000000001</v>
+        <v>74.965</v>
       </c>
       <c r="G30">
         <v>25.2</v>
@@ -3747,28 +3747,28 @@
         <v>50.425</v>
       </c>
       <c r="M30">
-        <v>3.640714</v>
+        <v>3.7707395</v>
       </c>
       <c r="N30">
-        <v>46.78428599999999</v>
+        <v>46.6542605</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>46.78428599999999</v>
+        <v>46.6542605</v>
       </c>
       <c r="Q30">
-        <v>54.484286</v>
+        <v>54.3542605</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1367677189166116</v>
+        <v>0.1380489543943104</v>
       </c>
       <c r="T30">
-        <v>1.773130159810941</v>
+        <v>1.79810382403363</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>13.85030518738906</v>
+        <v>13.37270845678944</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1126017576199604</v>
+        <v>0.1126467576199604</v>
       </c>
       <c r="C31">
-        <v>193.1295052285825</v>
+        <v>190.4676771971669</v>
       </c>
       <c r="D31">
-        <v>242.8945052285825</v>
+        <v>242.817677197167</v>
       </c>
       <c r="E31">
-        <v>-44.83500000000001</v>
+        <v>-42.25</v>
       </c>
       <c r="F31">
-        <v>74.96499999999999</v>
+        <v>77.55</v>
       </c>
       <c r="G31">
         <v>25.2</v>
@@ -3829,28 +3829,28 @@
         <v>50.425</v>
       </c>
       <c r="M31">
-        <v>3.770739499999999</v>
+        <v>3.900765</v>
       </c>
       <c r="N31">
-        <v>46.6542605</v>
+        <v>46.524235</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>46.6542605</v>
+        <v>46.524235</v>
       </c>
       <c r="Q31">
-        <v>54.3542605</v>
+        <v>54.224235</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1380489543943104</v>
+        <v>0.1393667965999434</v>
       </c>
       <c r="T31">
-        <v>1.79810382403363</v>
+        <v>1.823791021519825</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>13.37270845678945</v>
+        <v>12.92695150822979</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1126467576199604</v>
+        <v>0.1131567576199604</v>
       </c>
       <c r="C32">
-        <v>190.4676771971669</v>
+        <v>187.0153440956777</v>
       </c>
       <c r="D32">
-        <v>242.817677197167</v>
+        <v>241.9503440956777</v>
       </c>
       <c r="E32">
-        <v>-42.25</v>
+        <v>-39.66499999999999</v>
       </c>
       <c r="F32">
-        <v>77.55</v>
+        <v>80.13500000000001</v>
       </c>
       <c r="G32">
         <v>25.2</v>
@@ -3911,45 +3911,45 @@
         <v>50.425</v>
       </c>
       <c r="M32">
-        <v>3.900765</v>
+        <v>4.150993000000001</v>
       </c>
       <c r="N32">
-        <v>46.524235</v>
+        <v>46.274007</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>46.524235</v>
+        <v>46.274007</v>
       </c>
       <c r="Q32">
-        <v>54.224235</v>
+        <v>53.974007</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1393667965999434</v>
+        <v>0.1407228371303774</v>
       </c>
       <c r="T32">
-        <v>1.823791021519825</v>
+        <v>1.850222775454895</v>
       </c>
       <c r="U32">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V32">
         <v>0</v>
       </c>
       <c r="W32">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y32">
-        <v>12.92695150822979</v>
+        <v>12.14769574412676</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1131567576199604</v>
+        <v>0.1132167576199604</v>
       </c>
       <c r="C33">
-        <v>187.0153440956777</v>
+        <v>184.3287120951365</v>
       </c>
       <c r="D33">
-        <v>241.9503440956777</v>
+        <v>241.8487120951364</v>
       </c>
       <c r="E33">
-        <v>-39.66499999999999</v>
+        <v>-37.08</v>
       </c>
       <c r="F33">
-        <v>80.13500000000001</v>
+        <v>82.72</v>
       </c>
       <c r="G33">
         <v>25.2</v>
@@ -3993,28 +3993,28 @@
         <v>50.425</v>
       </c>
       <c r="M33">
-        <v>4.150993000000001</v>
+        <v>4.284896</v>
       </c>
       <c r="N33">
-        <v>46.274007</v>
+        <v>46.14010399999999</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>46.274007</v>
+        <v>46.14010399999999</v>
       </c>
       <c r="Q33">
-        <v>53.974007</v>
+        <v>53.840104</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1407228371303774</v>
+        <v>0.1421187612058241</v>
       </c>
       <c r="T33">
-        <v>1.850222775454895</v>
+        <v>1.877431933917467</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>12.14769574412676</v>
+        <v>11.7680802521228</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1132167576199604</v>
+        <v>0.1132767576199604</v>
       </c>
       <c r="C34">
-        <v>184.3287120951365</v>
+        <v>181.6421654404263</v>
       </c>
       <c r="D34">
-        <v>241.8487120951364</v>
+        <v>241.7471654404263</v>
       </c>
       <c r="E34">
-        <v>-37.08</v>
+        <v>-34.49499999999999</v>
       </c>
       <c r="F34">
-        <v>82.72</v>
+        <v>85.30500000000001</v>
       </c>
       <c r="G34">
         <v>25.2</v>
@@ -4075,28 +4075,28 @@
         <v>50.425</v>
       </c>
       <c r="M34">
-        <v>4.284896</v>
+        <v>4.418799</v>
       </c>
       <c r="N34">
-        <v>46.14010399999999</v>
+        <v>46.006201</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>46.14010399999999</v>
+        <v>46.006201</v>
       </c>
       <c r="Q34">
-        <v>53.840104</v>
+        <v>53.706201</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1421187612058241</v>
+        <v>0.1435563546566573</v>
       </c>
       <c r="T34">
-        <v>1.877431933917467</v>
+        <v>1.905453306065489</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>11.7680802521228</v>
+        <v>11.41147175963424</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1132767576199604</v>
+        <v>0.1133367576199604</v>
       </c>
       <c r="C35">
-        <v>181.6421654404263</v>
+        <v>178.9557040240883</v>
       </c>
       <c r="D35">
-        <v>241.7471654404263</v>
+        <v>241.6457040240882</v>
       </c>
       <c r="E35">
-        <v>-34.49499999999999</v>
+        <v>-31.91</v>
       </c>
       <c r="F35">
-        <v>85.30500000000001</v>
+        <v>87.89</v>
       </c>
       <c r="G35">
         <v>25.2</v>
@@ -4157,28 +4157,28 @@
         <v>50.425</v>
       </c>
       <c r="M35">
-        <v>4.418799</v>
+        <v>4.552702</v>
       </c>
       <c r="N35">
-        <v>46.006201</v>
+        <v>45.872298</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>46.006201</v>
+        <v>45.872298</v>
       </c>
       <c r="Q35">
-        <v>53.706201</v>
+        <v>53.572298</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1435563546566573</v>
+        <v>0.1450375115453945</v>
       </c>
       <c r="T35">
-        <v>1.905453306065489</v>
+        <v>1.934323810702844</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.41147175963424</v>
+        <v>11.07584023729205</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1133367576199604</v>
+        <v>0.1133967576199604</v>
       </c>
       <c r="C36">
-        <v>178.9557040240883</v>
+        <v>176.2693277388434</v>
       </c>
       <c r="D36">
-        <v>241.6457040240882</v>
+        <v>241.5443277388434</v>
       </c>
       <c r="E36">
-        <v>-31.91</v>
+        <v>-29.32499999999999</v>
       </c>
       <c r="F36">
-        <v>87.89</v>
+        <v>90.47500000000001</v>
       </c>
       <c r="G36">
         <v>25.2</v>
@@ -4239,28 +4239,28 @@
         <v>50.425</v>
       </c>
       <c r="M36">
-        <v>4.552702</v>
+        <v>4.686605</v>
       </c>
       <c r="N36">
-        <v>45.872298</v>
+        <v>45.738395</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>45.872298</v>
+        <v>45.738395</v>
       </c>
       <c r="Q36">
-        <v>53.572298</v>
+        <v>53.438395</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1450375115453945</v>
+        <v>0.1465642424922468</v>
       </c>
       <c r="T36">
-        <v>1.934323810702844</v>
+        <v>1.964082638559811</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.07584023729205</v>
+        <v>10.75938765908371</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1133967576199604</v>
+        <v>0.1134567576199604</v>
       </c>
       <c r="C37">
-        <v>176.2693277388434</v>
+        <v>173.5830364775931</v>
       </c>
       <c r="D37">
-        <v>241.5443277388434</v>
+        <v>241.4430364775931</v>
       </c>
       <c r="E37">
-        <v>-29.32499999999999</v>
+        <v>-26.73999999999998</v>
       </c>
       <c r="F37">
-        <v>90.47500000000001</v>
+        <v>93.06000000000002</v>
       </c>
       <c r="G37">
         <v>25.2</v>
@@ -4321,28 +4321,28 @@
         <v>50.425</v>
       </c>
       <c r="M37">
-        <v>4.686605</v>
+        <v>4.820508000000001</v>
       </c>
       <c r="N37">
-        <v>45.738395</v>
+        <v>45.60449199999999</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>45.738395</v>
+        <v>45.60449199999999</v>
       </c>
       <c r="Q37">
-        <v>53.438395</v>
+        <v>53.304492</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1465642424922468</v>
+        <v>0.1481386837811881</v>
       </c>
       <c r="T37">
-        <v>1.964082638559811</v>
+        <v>1.994771429787308</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>10.75938765908371</v>
+        <v>10.46051577966471</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1134567576199604</v>
+        <v>0.1135167576199604</v>
       </c>
       <c r="C38">
-        <v>173.5830364775931</v>
+        <v>170.896830133418</v>
       </c>
       <c r="D38">
-        <v>241.4430364775931</v>
+        <v>241.341830133418</v>
       </c>
       <c r="E38">
-        <v>-26.73999999999999</v>
+        <v>-24.155</v>
       </c>
       <c r="F38">
-        <v>93.06</v>
+        <v>95.645</v>
       </c>
       <c r="G38">
         <v>25.2</v>
@@ -4403,28 +4403,28 @@
         <v>50.425</v>
       </c>
       <c r="M38">
-        <v>4.820508</v>
+        <v>4.954410999999999</v>
       </c>
       <c r="N38">
-        <v>45.60449199999999</v>
+        <v>45.470589</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>45.60449199999999</v>
+        <v>45.470589</v>
       </c>
       <c r="Q38">
-        <v>53.304492</v>
+        <v>53.170589</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1481386837811881</v>
+        <v>0.1497631073332704</v>
       </c>
       <c r="T38">
-        <v>1.994771429787308</v>
+        <v>2.026434468355361</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.46051577966471</v>
+        <v>10.17779913697107</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1135167576199604</v>
+        <v>0.1135767576199604</v>
       </c>
       <c r="C39">
-        <v>170.896830133418</v>
+        <v>168.2107085995781</v>
       </c>
       <c r="D39">
-        <v>241.341830133418</v>
+        <v>241.2407085995782</v>
       </c>
       <c r="E39">
-        <v>-24.155</v>
+        <v>-21.56999999999999</v>
       </c>
       <c r="F39">
-        <v>95.645</v>
+        <v>98.23</v>
       </c>
       <c r="G39">
         <v>25.2</v>
@@ -4485,28 +4485,28 @@
         <v>50.425</v>
       </c>
       <c r="M39">
-        <v>4.954410999999999</v>
+        <v>5.088314</v>
       </c>
       <c r="N39">
-        <v>45.470589</v>
+        <v>45.336686</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>45.470589</v>
+        <v>45.336686</v>
       </c>
       <c r="Q39">
-        <v>53.170589</v>
+        <v>53.036686</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1497631073332704</v>
+        <v>0.1514399316450974</v>
       </c>
       <c r="T39">
-        <v>2.026434468355361</v>
+        <v>2.059118895264318</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.17779913697107</v>
+        <v>9.909962317577099</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1135767576199604</v>
+        <v>0.1142997576199604</v>
       </c>
       <c r="C40">
-        <v>168.2107085995781</v>
+        <v>164.4138233768409</v>
       </c>
       <c r="D40">
-        <v>241.2407085995782</v>
+        <v>240.0288233768409</v>
       </c>
       <c r="E40">
-        <v>-21.56999999999999</v>
+        <v>-18.985</v>
       </c>
       <c r="F40">
-        <v>98.23</v>
+        <v>100.815</v>
       </c>
       <c r="G40">
         <v>25.2</v>
@@ -4567,45 +4567,45 @@
         <v>50.425</v>
       </c>
       <c r="M40">
-        <v>5.088314</v>
+        <v>5.3936025</v>
       </c>
       <c r="N40">
-        <v>45.336686</v>
+        <v>45.0313975</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>45.336686</v>
+        <v>45.0313975</v>
       </c>
       <c r="Q40">
-        <v>53.036686</v>
+        <v>52.7313975</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1514399316450974</v>
+        <v>0.1531717338032137</v>
       </c>
       <c r="T40">
-        <v>2.059118895264318</v>
+        <v>2.092874942727668</v>
       </c>
       <c r="U40">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V40">
         <v>0</v>
       </c>
       <c r="W40">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>9.909962317577099</v>
+        <v>9.349038977195669</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1142997576199604</v>
+        <v>0.1143767576199604</v>
       </c>
       <c r="C41">
-        <v>164.4138233768409</v>
+        <v>161.7004738038915</v>
       </c>
       <c r="D41">
-        <v>240.0288233768409</v>
+        <v>239.9004738038915</v>
       </c>
       <c r="E41">
-        <v>-18.985</v>
+        <v>-16.39999999999999</v>
       </c>
       <c r="F41">
-        <v>100.815</v>
+        <v>103.4</v>
       </c>
       <c r="G41">
         <v>25.2</v>
@@ -4649,28 +4649,28 @@
         <v>50.425</v>
       </c>
       <c r="M41">
-        <v>5.3936025</v>
+        <v>5.5319</v>
       </c>
       <c r="N41">
-        <v>45.0313975</v>
+        <v>44.8931</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>45.0313975</v>
+        <v>44.8931</v>
       </c>
       <c r="Q41">
-        <v>52.7313975</v>
+        <v>52.5931</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1531717338032137</v>
+        <v>0.154961262699934</v>
       </c>
       <c r="T41">
-        <v>2.092874942727668</v>
+        <v>2.127756191773129</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>9.349038977195669</v>
+        <v>9.115313002765776</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1143767576199604</v>
+        <v>0.1144537576199604</v>
       </c>
       <c r="C42">
-        <v>161.7004738038915</v>
+        <v>158.9872614212052</v>
       </c>
       <c r="D42">
-        <v>239.9004738038915</v>
+        <v>239.7722614212052</v>
       </c>
       <c r="E42">
-        <v>-16.39999999999999</v>
+        <v>-13.81499999999998</v>
       </c>
       <c r="F42">
-        <v>103.4</v>
+        <v>105.985</v>
       </c>
       <c r="G42">
         <v>25.2</v>
@@ -4731,28 +4731,28 @@
         <v>50.425</v>
       </c>
       <c r="M42">
-        <v>5.5319</v>
+        <v>5.6701975</v>
       </c>
       <c r="N42">
-        <v>44.8931</v>
+        <v>44.7548025</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>44.8931</v>
+        <v>44.7548025</v>
       </c>
       <c r="Q42">
-        <v>52.5931</v>
+        <v>52.4548025</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.154961262699934</v>
+        <v>0.1568114535931532</v>
       </c>
       <c r="T42">
-        <v>2.127756191773129</v>
+        <v>2.16381985604047</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>9.115313002765776</v>
+        <v>8.892988295381244</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1144537576199604</v>
+        <v>0.1145307576199604</v>
       </c>
       <c r="C43">
-        <v>158.9872614212052</v>
+        <v>156.2741860089397</v>
       </c>
       <c r="D43">
-        <v>239.7722614212052</v>
+        <v>239.6441860089397</v>
       </c>
       <c r="E43">
-        <v>-13.81499999999998</v>
+        <v>-11.22999999999999</v>
       </c>
       <c r="F43">
-        <v>105.985</v>
+        <v>108.57</v>
       </c>
       <c r="G43">
         <v>25.2</v>
@@ -4813,28 +4813,28 @@
         <v>50.425</v>
       </c>
       <c r="M43">
-        <v>5.6701975</v>
+        <v>5.808495000000001</v>
       </c>
       <c r="N43">
-        <v>44.7548025</v>
+        <v>44.616505</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>44.7548025</v>
+        <v>44.616505</v>
       </c>
       <c r="Q43">
-        <v>52.4548025</v>
+        <v>52.316505</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1568114535931532</v>
+        <v>0.1587254441723455</v>
       </c>
       <c r="T43">
-        <v>2.16381985604047</v>
+        <v>2.20112709493772</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.892988295381244</v>
+        <v>8.681250478824548</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1145307576199604</v>
+        <v>0.1146077576199604</v>
       </c>
       <c r="C44">
-        <v>156.2741860089397</v>
+        <v>153.5612473477221</v>
       </c>
       <c r="D44">
-        <v>239.6441860089397</v>
+        <v>239.5162473477221</v>
       </c>
       <c r="E44">
-        <v>-11.23</v>
+        <v>-8.644999999999996</v>
       </c>
       <c r="F44">
-        <v>108.57</v>
+        <v>111.155</v>
       </c>
       <c r="G44">
         <v>25.2</v>
@@ -4895,28 +4895,28 @@
         <v>50.425</v>
       </c>
       <c r="M44">
-        <v>5.808495</v>
+        <v>5.9467925</v>
       </c>
       <c r="N44">
-        <v>44.616505</v>
+        <v>44.4782075</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>44.616505</v>
+        <v>44.4782075</v>
       </c>
       <c r="Q44">
-        <v>52.316505</v>
+        <v>52.1782075</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1587254441723455</v>
+        <v>0.16070659231572</v>
       </c>
       <c r="T44">
-        <v>2.201127094937719</v>
+        <v>2.239743359761188</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.681250478824548</v>
+        <v>8.479360932805374</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1146077576199604</v>
+        <v>0.1146847576199604</v>
       </c>
       <c r="C45">
-        <v>153.5612473477221</v>
+        <v>150.8484452186477</v>
       </c>
       <c r="D45">
-        <v>239.5162473477221</v>
+        <v>239.3884452186477</v>
       </c>
       <c r="E45">
-        <v>-8.644999999999996</v>
+        <v>-6.060000000000002</v>
       </c>
       <c r="F45">
-        <v>111.155</v>
+        <v>113.74</v>
       </c>
       <c r="G45">
         <v>25.2</v>
@@ -4977,28 +4977,28 @@
         <v>50.425</v>
       </c>
       <c r="M45">
-        <v>5.9467925</v>
+        <v>6.085089999999999</v>
       </c>
       <c r="N45">
-        <v>44.4782075</v>
+        <v>44.33991</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>44.4782075</v>
+        <v>44.33991</v>
       </c>
       <c r="Q45">
-        <v>52.1782075</v>
+        <v>52.03991</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.16070659231572</v>
+        <v>0.1627584957499292</v>
       </c>
       <c r="T45">
-        <v>2.239743359761188</v>
+        <v>2.279738776899781</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.479360932805374</v>
+        <v>8.286648184332524</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1146847576199604</v>
+        <v>0.1147617576199604</v>
       </c>
       <c r="C46">
-        <v>150.8484452186477</v>
+        <v>148.1357794032789</v>
       </c>
       <c r="D46">
-        <v>239.3884452186477</v>
+        <v>239.2607794032789</v>
       </c>
       <c r="E46">
-        <v>-6.060000000000002</v>
+        <v>-3.474999999999994</v>
       </c>
       <c r="F46">
-        <v>113.74</v>
+        <v>116.325</v>
       </c>
       <c r="G46">
         <v>25.2</v>
@@ -5059,28 +5059,28 @@
         <v>50.425</v>
       </c>
       <c r="M46">
-        <v>6.085089999999999</v>
+        <v>6.2233875</v>
       </c>
       <c r="N46">
-        <v>44.33991</v>
+        <v>44.2016125</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>44.33991</v>
+        <v>44.2016125</v>
       </c>
       <c r="Q46">
-        <v>52.03991</v>
+        <v>51.9016125</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1627584957499292</v>
+        <v>0.1648850138544734</v>
       </c>
       <c r="T46">
-        <v>2.279738776899781</v>
+        <v>2.321188572843413</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.286648184332524</v>
+        <v>8.102500446902912</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1147617576199604</v>
+        <v>0.1148387576199604</v>
       </c>
       <c r="C47">
-        <v>148.1357794032789</v>
+        <v>145.4232496836436</v>
       </c>
       <c r="D47">
-        <v>239.2607794032789</v>
+        <v>239.1332496836436</v>
       </c>
       <c r="E47">
-        <v>-3.474999999999994</v>
+        <v>-0.8899999999999864</v>
       </c>
       <c r="F47">
-        <v>116.325</v>
+        <v>118.91</v>
       </c>
       <c r="G47">
         <v>25.2</v>
@@ -5141,28 +5141,28 @@
         <v>50.425</v>
       </c>
       <c r="M47">
-        <v>6.2233875</v>
+        <v>6.361685</v>
       </c>
       <c r="N47">
-        <v>44.2016125</v>
+        <v>44.063315</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>44.2016125</v>
+        <v>44.063315</v>
       </c>
       <c r="Q47">
-        <v>51.9016125</v>
+        <v>51.763315</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1648850138544734</v>
+        <v>0.1670902918888155</v>
       </c>
       <c r="T47">
-        <v>2.321188572843413</v>
+        <v>2.364173546414587</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.102500446902912</v>
+        <v>7.926359132839805</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1148387576199604</v>
+        <v>0.1149157576199604</v>
       </c>
       <c r="C48">
-        <v>145.4232496836436</v>
+        <v>142.7108558422344</v>
       </c>
       <c r="D48">
-        <v>239.1332496836436</v>
+        <v>239.0058558422344</v>
       </c>
       <c r="E48">
-        <v>-0.8899999999999864</v>
+        <v>1.695000000000007</v>
       </c>
       <c r="F48">
-        <v>118.91</v>
+        <v>121.495</v>
       </c>
       <c r="G48">
         <v>25.2</v>
@@ -5223,28 +5223,28 @@
         <v>50.425</v>
       </c>
       <c r="M48">
-        <v>6.361685</v>
+        <v>6.4999825</v>
       </c>
       <c r="N48">
-        <v>44.063315</v>
+        <v>43.9250175</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>44.063315</v>
+        <v>43.9250175</v>
       </c>
       <c r="Q48">
-        <v>51.763315</v>
+        <v>51.6250175</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1670902918888155</v>
+        <v>0.1693787879621894</v>
       </c>
       <c r="T48">
-        <v>2.364173546414587</v>
+        <v>2.408780594460146</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.926359132839805</v>
+        <v>7.757713193843213</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1149157576199604</v>
+        <v>0.1153767576199604</v>
       </c>
       <c r="C49">
-        <v>142.7108558422344</v>
+        <v>139.3659771892086</v>
       </c>
       <c r="D49">
-        <v>239.0058558422344</v>
+        <v>238.2459771892086</v>
       </c>
       <c r="E49">
-        <v>1.695000000000007</v>
+        <v>4.280000000000015</v>
       </c>
       <c r="F49">
-        <v>121.495</v>
+        <v>124.08</v>
       </c>
       <c r="G49">
         <v>25.2</v>
@@ -5305,45 +5305,45 @@
         <v>50.425</v>
       </c>
       <c r="M49">
-        <v>6.4999825</v>
+        <v>6.737544000000001</v>
       </c>
       <c r="N49">
-        <v>43.9250175</v>
+        <v>43.687456</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>43.9250175</v>
+        <v>43.687456</v>
       </c>
       <c r="Q49">
-        <v>51.6250175</v>
+        <v>51.387456</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1693787879621894</v>
+        <v>0.1717553031153084</v>
       </c>
       <c r="T49">
-        <v>2.408780594460146</v>
+        <v>2.455103298199764</v>
       </c>
       <c r="U49">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V49">
         <v>0</v>
       </c>
       <c r="W49">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y49">
-        <v>7.757713193843213</v>
+        <v>7.484181179373373</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1153767576199604</v>
+        <v>0.1154617576199604</v>
       </c>
       <c r="C50">
-        <v>139.3659771892086</v>
+        <v>136.641396684072</v>
       </c>
       <c r="D50">
-        <v>238.2459771892086</v>
+        <v>238.1063966840719</v>
       </c>
       <c r="E50">
-        <v>4.280000000000001</v>
+        <v>6.864999999999995</v>
       </c>
       <c r="F50">
-        <v>124.08</v>
+        <v>126.665</v>
       </c>
       <c r="G50">
         <v>25.2</v>
@@ -5387,28 +5387,28 @@
         <v>50.425</v>
       </c>
       <c r="M50">
-        <v>6.737544</v>
+        <v>6.877909499999999</v>
       </c>
       <c r="N50">
-        <v>43.687456</v>
+        <v>43.5470905</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>43.687456</v>
+        <v>43.5470905</v>
       </c>
       <c r="Q50">
-        <v>51.387456</v>
+        <v>51.2470905</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1717553031153084</v>
+        <v>0.1742250149410988</v>
       </c>
       <c r="T50">
-        <v>2.455103298199764</v>
+        <v>2.503242578556622</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.484181179373373</v>
+        <v>7.331442787957591</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1154617576199604</v>
+        <v>0.1155467576199604</v>
       </c>
       <c r="C51">
-        <v>136.641396684072</v>
+        <v>133.9169796344532</v>
       </c>
       <c r="D51">
-        <v>238.1063966840719</v>
+        <v>237.9669796344533</v>
       </c>
       <c r="E51">
-        <v>6.864999999999995</v>
+        <v>9.450000000000003</v>
       </c>
       <c r="F51">
-        <v>126.665</v>
+        <v>129.25</v>
       </c>
       <c r="G51">
         <v>25.2</v>
@@ -5469,28 +5469,28 @@
         <v>50.425</v>
       </c>
       <c r="M51">
-        <v>6.877909499999999</v>
+        <v>7.018275</v>
       </c>
       <c r="N51">
-        <v>43.5470905</v>
+        <v>43.40672499999999</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>43.5470905</v>
+        <v>43.40672499999999</v>
       </c>
       <c r="Q51">
-        <v>51.2470905</v>
+        <v>51.106725</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1742250149410988</v>
+        <v>0.1767935152399208</v>
       </c>
       <c r="T51">
-        <v>2.503242578556622</v>
+        <v>2.553307430127755</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>7.331442787957591</v>
+        <v>7.184813932198439</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1155467576199604</v>
+        <v>0.1156317576199604</v>
       </c>
       <c r="C52">
-        <v>133.9169796344532</v>
+        <v>131.1927257533991</v>
       </c>
       <c r="D52">
-        <v>237.9669796344533</v>
+        <v>237.8277257533991</v>
       </c>
       <c r="E52">
-        <v>9.450000000000003</v>
+        <v>12.03500000000001</v>
       </c>
       <c r="F52">
-        <v>129.25</v>
+        <v>131.835</v>
       </c>
       <c r="G52">
         <v>25.2</v>
@@ -5551,28 +5551,28 @@
         <v>50.425</v>
       </c>
       <c r="M52">
-        <v>7.018275</v>
+        <v>7.158640500000001</v>
       </c>
       <c r="N52">
-        <v>43.40672499999999</v>
+        <v>43.26635949999999</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>43.40672499999999</v>
+        <v>43.26635949999999</v>
       </c>
       <c r="Q52">
-        <v>51.106725</v>
+        <v>50.9663595</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1767935152399208</v>
+        <v>0.1794668522856334</v>
       </c>
       <c r="T52">
-        <v>2.553307430127755</v>
+        <v>2.605415745028321</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.184813932198439</v>
+        <v>7.043935227645527</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1156317576199604</v>
+        <v>0.1157167576199604</v>
       </c>
       <c r="C53">
-        <v>131.1927257533991</v>
+        <v>128.4686347546275</v>
       </c>
       <c r="D53">
-        <v>237.8277257533991</v>
+        <v>237.6886347546275</v>
       </c>
       <c r="E53">
-        <v>12.03500000000001</v>
+        <v>14.62000000000002</v>
       </c>
       <c r="F53">
-        <v>131.835</v>
+        <v>134.42</v>
       </c>
       <c r="G53">
         <v>25.2</v>
@@ -5633,28 +5633,28 @@
         <v>50.425</v>
       </c>
       <c r="M53">
-        <v>7.158640500000001</v>
+        <v>7.299006000000001</v>
       </c>
       <c r="N53">
-        <v>43.26635949999999</v>
+        <v>43.125994</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
       <c r="P53">
-        <v>43.26635949999999</v>
+        <v>43.125994</v>
       </c>
       <c r="Q53">
-        <v>50.9663595</v>
+        <v>50.825994</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1794668522856334</v>
+        <v>0.1822515783749175</v>
       </c>
       <c r="T53">
-        <v>2.605415745028321</v>
+        <v>2.659695239716411</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.043935227645527</v>
+        <v>6.908474934806191</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1157167576199604</v>
+        <v>0.1158017576199604</v>
       </c>
       <c r="C54">
-        <v>128.4686347546275</v>
+        <v>125.7447063525254</v>
       </c>
       <c r="D54">
-        <v>237.6886347546275</v>
+        <v>237.5497063525254</v>
       </c>
       <c r="E54">
-        <v>14.62000000000002</v>
+        <v>17.205</v>
       </c>
       <c r="F54">
-        <v>134.42</v>
+        <v>137.005</v>
       </c>
       <c r="G54">
         <v>25.2</v>
@@ -5715,28 +5715,28 @@
         <v>50.425</v>
       </c>
       <c r="M54">
-        <v>7.299006000000001</v>
+        <v>7.4393715</v>
       </c>
       <c r="N54">
-        <v>43.125994</v>
+        <v>42.9856285</v>
       </c>
       <c r="O54">
         <v>0</v>
       </c>
       <c r="P54">
-        <v>43.125994</v>
+        <v>42.9856285</v>
       </c>
       <c r="Q54">
-        <v>50.825994</v>
+        <v>50.6856285</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1822515783749175</v>
+        <v>0.1851548034467242</v>
       </c>
       <c r="T54">
-        <v>2.659695239716411</v>
+        <v>2.716284500135909</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.908474934806191</v>
+        <v>6.778126351130602</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1158017576199604</v>
+        <v>0.1158867576199604</v>
       </c>
       <c r="C55">
-        <v>125.7447063525254</v>
+        <v>123.0209402621475</v>
       </c>
       <c r="D55">
-        <v>237.5497063525254</v>
+        <v>237.4109402621476</v>
       </c>
       <c r="E55">
-        <v>17.205</v>
+        <v>19.79000000000001</v>
       </c>
       <c r="F55">
-        <v>137.005</v>
+        <v>139.59</v>
       </c>
       <c r="G55">
         <v>25.2</v>
@@ -5797,28 +5797,28 @@
         <v>50.425</v>
       </c>
       <c r="M55">
-        <v>7.4393715</v>
+        <v>7.579737000000001</v>
       </c>
       <c r="N55">
-        <v>42.9856285</v>
+        <v>42.845263</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
       <c r="P55">
-        <v>42.9856285</v>
+        <v>42.845263</v>
       </c>
       <c r="Q55">
-        <v>50.6856285</v>
+        <v>50.545263</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1851548034467242</v>
+        <v>0.188184255695566</v>
       </c>
       <c r="T55">
-        <v>2.716284500135909</v>
+        <v>2.775334163182342</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.778126351130602</v>
+        <v>6.652605492776331</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1158867576199604</v>
+        <v>0.1159717576199604</v>
       </c>
       <c r="C56">
-        <v>123.0209402621475</v>
+        <v>120.2973361992136</v>
       </c>
       <c r="D56">
-        <v>237.4109402621476</v>
+        <v>237.2723361992136</v>
       </c>
       <c r="E56">
-        <v>19.79000000000001</v>
+        <v>22.37500000000001</v>
       </c>
       <c r="F56">
-        <v>139.59</v>
+        <v>142.175</v>
       </c>
       <c r="G56">
         <v>25.2</v>
@@ -5879,28 +5879,28 @@
         <v>50.425</v>
       </c>
       <c r="M56">
-        <v>7.579737000000001</v>
+        <v>7.720102500000001</v>
       </c>
       <c r="N56">
-        <v>42.845263</v>
+        <v>42.70489749999999</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>42.845263</v>
+        <v>42.70489749999999</v>
       </c>
       <c r="Q56">
-        <v>50.545263</v>
+        <v>50.4048975</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.188184255695566</v>
+        <v>0.1913483502665786</v>
       </c>
       <c r="T56">
-        <v>2.775334163182342</v>
+        <v>2.837008255697505</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.652605492776331</v>
+        <v>6.531649029271307</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1159717576199604</v>
+        <v>0.1160567576199604</v>
       </c>
       <c r="C57">
-        <v>120.2973361992136</v>
+        <v>117.5738938801073</v>
       </c>
       <c r="D57">
-        <v>237.2723361992136</v>
+        <v>237.1338938801073</v>
       </c>
       <c r="E57">
-        <v>22.37500000000001</v>
+        <v>24.96000000000002</v>
       </c>
       <c r="F57">
-        <v>142.175</v>
+        <v>144.76</v>
       </c>
       <c r="G57">
         <v>25.2</v>
@@ -5961,28 +5961,28 @@
         <v>50.425</v>
       </c>
       <c r="M57">
-        <v>7.720102500000001</v>
+        <v>7.860468000000001</v>
       </c>
       <c r="N57">
-        <v>42.70489749999999</v>
+        <v>42.564532</v>
       </c>
       <c r="O57">
         <v>0</v>
       </c>
       <c r="P57">
-        <v>42.70489749999999</v>
+        <v>42.564532</v>
       </c>
       <c r="Q57">
-        <v>50.4048975</v>
+        <v>50.264532</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1913483502665786</v>
+        <v>0.1946562673180918</v>
       </c>
       <c r="T57">
-        <v>2.837008255697505</v>
+        <v>2.901485716054267</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.531649029271307</v>
+        <v>6.415012439462892</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1160567576199604</v>
+        <v>0.1161417576199604</v>
       </c>
       <c r="C58">
-        <v>117.5738938801073</v>
+        <v>114.8506130218735</v>
       </c>
       <c r="D58">
-        <v>237.1338938801073</v>
+        <v>236.9956130218735</v>
       </c>
       <c r="E58">
-        <v>24.96000000000002</v>
+        <v>27.54500000000003</v>
       </c>
       <c r="F58">
-        <v>144.76</v>
+        <v>147.345</v>
       </c>
       <c r="G58">
         <v>25.2</v>
@@ -6043,28 +6043,28 @@
         <v>50.425</v>
       </c>
       <c r="M58">
-        <v>7.860468000000001</v>
+        <v>8.000833500000002</v>
       </c>
       <c r="N58">
-        <v>42.564532</v>
+        <v>42.4241665</v>
       </c>
       <c r="O58">
         <v>0</v>
       </c>
       <c r="P58">
-        <v>42.564532</v>
+        <v>42.4241665</v>
       </c>
       <c r="Q58">
-        <v>50.264532</v>
+        <v>50.1241665</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1946562673180918</v>
+        <v>0.1981180409766521</v>
       </c>
       <c r="T58">
-        <v>2.901485716054267</v>
+        <v>2.968962128055529</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.415012439462892</v>
+        <v>6.302468361577576</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1161417576199604</v>
+        <v>0.1162267576199604</v>
       </c>
       <c r="C59">
-        <v>114.8506130218735</v>
+        <v>112.1274933422168</v>
       </c>
       <c r="D59">
-        <v>236.9956130218735</v>
+        <v>236.8574933422168</v>
       </c>
       <c r="E59">
-        <v>27.54500000000003</v>
+        <v>30.13000000000001</v>
       </c>
       <c r="F59">
-        <v>147.345</v>
+        <v>149.93</v>
       </c>
       <c r="G59">
         <v>25.2</v>
@@ -6125,28 +6125,28 @@
         <v>50.425</v>
       </c>
       <c r="M59">
-        <v>8.000833500000002</v>
+        <v>8.141199</v>
       </c>
       <c r="N59">
-        <v>42.4241665</v>
+        <v>42.283801</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>42.4241665</v>
+        <v>42.283801</v>
       </c>
       <c r="Q59">
-        <v>50.1241665</v>
+        <v>49.983801</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1981180409766521</v>
+        <v>0.2017446609999057</v>
       </c>
       <c r="T59">
-        <v>2.968962128055529</v>
+        <v>3.039651702533042</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.302468361577576</v>
+        <v>6.193805113964171</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1162267576199604</v>
+        <v>0.1169017576199604</v>
       </c>
       <c r="C60">
-        <v>112.1274933422168</v>
+        <v>108.4513497110562</v>
       </c>
       <c r="D60">
-        <v>236.8574933422168</v>
+        <v>235.7663497110562</v>
       </c>
       <c r="E60">
-        <v>30.12999999999998</v>
+        <v>32.71499999999999</v>
       </c>
       <c r="F60">
-        <v>149.93</v>
+        <v>152.515</v>
       </c>
       <c r="G60">
         <v>25.2</v>
@@ -6207,45 +6207,45 @@
         <v>50.425</v>
       </c>
       <c r="M60">
-        <v>8.141198999999999</v>
+        <v>8.434079499999999</v>
       </c>
       <c r="N60">
-        <v>42.283801</v>
+        <v>41.9909205</v>
       </c>
       <c r="O60">
         <v>0</v>
       </c>
       <c r="P60">
-        <v>42.283801</v>
+        <v>41.9909205</v>
       </c>
       <c r="Q60">
-        <v>49.983801</v>
+        <v>49.6909205</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2017446609999056</v>
+        <v>0.2055481893169765</v>
       </c>
       <c r="T60">
-        <v>3.03965170253304</v>
+        <v>3.113789548936285</v>
       </c>
       <c r="U60">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V60">
         <v>0</v>
       </c>
       <c r="W60">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>6.193805113964173</v>
+        <v>5.978720025107661</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1169017576199604</v>
+        <v>0.1169967576199604</v>
       </c>
       <c r="C61">
-        <v>108.4513497110562</v>
+        <v>105.7135878437724</v>
       </c>
       <c r="D61">
-        <v>235.7663497110562</v>
+        <v>235.6135878437724</v>
       </c>
       <c r="E61">
-        <v>32.71499999999999</v>
+        <v>35.3</v>
       </c>
       <c r="F61">
-        <v>152.515</v>
+        <v>155.1</v>
       </c>
       <c r="G61">
         <v>25.2</v>
@@ -6289,28 +6289,28 @@
         <v>50.425</v>
       </c>
       <c r="M61">
-        <v>8.434079499999999</v>
+        <v>8.577030000000001</v>
       </c>
       <c r="N61">
-        <v>41.9909205</v>
+        <v>41.84797</v>
       </c>
       <c r="O61">
         <v>0</v>
       </c>
       <c r="P61">
-        <v>41.9909205</v>
+        <v>41.84797</v>
       </c>
       <c r="Q61">
-        <v>49.6909205</v>
+        <v>49.54797</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2055481893169765</v>
+        <v>0.209541894049901</v>
       </c>
       <c r="T61">
-        <v>3.113789548936285</v>
+        <v>3.191634287659693</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.978720025107661</v>
+        <v>5.879074691355865</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1169967576199604</v>
+        <v>0.1170917576199604</v>
       </c>
       <c r="C62">
-        <v>105.7135878437724</v>
+        <v>102.9760238086009</v>
       </c>
       <c r="D62">
-        <v>235.6135878437724</v>
+        <v>235.4610238086009</v>
       </c>
       <c r="E62">
-        <v>35.3</v>
+        <v>37.88500000000001</v>
       </c>
       <c r="F62">
-        <v>155.1</v>
+        <v>157.685</v>
       </c>
       <c r="G62">
         <v>25.2</v>
@@ -6371,28 +6371,28 @@
         <v>50.425</v>
       </c>
       <c r="M62">
-        <v>8.577030000000001</v>
+        <v>8.7199805</v>
       </c>
       <c r="N62">
-        <v>41.84797</v>
+        <v>41.7050195</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>41.84797</v>
+        <v>41.7050195</v>
       </c>
       <c r="Q62">
-        <v>49.54797</v>
+        <v>49.4050195</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.209541894049901</v>
+        <v>0.2137404041537445</v>
       </c>
       <c r="T62">
-        <v>3.191634287659693</v>
+        <v>3.273471064266352</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.879074691355865</v>
+        <v>5.782696417727081</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1170917576199604</v>
+        <v>0.1171867576199604</v>
       </c>
       <c r="C63">
-        <v>102.9760238086009</v>
+        <v>100.238657221491</v>
       </c>
       <c r="D63">
-        <v>235.4610238086009</v>
+        <v>235.308657221491</v>
       </c>
       <c r="E63">
-        <v>37.88500000000001</v>
+        <v>40.47000000000001</v>
       </c>
       <c r="F63">
-        <v>157.685</v>
+        <v>160.27</v>
       </c>
       <c r="G63">
         <v>25.2</v>
@@ -6453,28 +6453,28 @@
         <v>50.425</v>
       </c>
       <c r="M63">
-        <v>8.7199805</v>
+        <v>8.862931000000001</v>
       </c>
       <c r="N63">
-        <v>41.7050195</v>
+        <v>41.56206899999999</v>
       </c>
       <c r="O63">
         <v>0</v>
       </c>
       <c r="P63">
-        <v>41.7050195</v>
+        <v>41.56206899999999</v>
       </c>
       <c r="Q63">
-        <v>49.4050195</v>
+        <v>49.262069</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2137404041537445</v>
+        <v>0.2181598884735799</v>
       </c>
       <c r="T63">
-        <v>3.273471064266352</v>
+        <v>3.359615039641783</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.782696417727081</v>
+        <v>5.689427120666966</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1171867576199604</v>
+        <v>0.1172817576199604</v>
       </c>
       <c r="C64">
-        <v>100.238657221491</v>
+        <v>97.50148769938508</v>
       </c>
       <c r="D64">
-        <v>235.308657221491</v>
+        <v>235.1564876993851</v>
       </c>
       <c r="E64">
-        <v>40.47000000000001</v>
+        <v>43.05499999999999</v>
       </c>
       <c r="F64">
-        <v>160.27</v>
+        <v>162.855</v>
       </c>
       <c r="G64">
         <v>25.2</v>
@@ -6535,28 +6535,28 @@
         <v>50.425</v>
       </c>
       <c r="M64">
-        <v>8.862931000000001</v>
+        <v>9.005881499999999</v>
       </c>
       <c r="N64">
-        <v>41.56206899999999</v>
+        <v>41.4191185</v>
       </c>
       <c r="O64">
         <v>0</v>
       </c>
       <c r="P64">
-        <v>41.56206899999999</v>
+        <v>41.4191185</v>
       </c>
       <c r="Q64">
-        <v>49.262069</v>
+        <v>49.1191185</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2181598884735799</v>
+        <v>0.2228182638377307</v>
       </c>
       <c r="T64">
-        <v>3.359615039641783</v>
+        <v>3.450415446118587</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.689427120666966</v>
+        <v>5.599118753672253</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1172817576199604</v>
+        <v>0.1173767576199604</v>
       </c>
       <c r="C65">
-        <v>97.50148769938508</v>
+        <v>94.76451486021597</v>
       </c>
       <c r="D65">
-        <v>235.1564876993851</v>
+        <v>235.004514860216</v>
       </c>
       <c r="E65">
-        <v>43.05499999999999</v>
+        <v>45.64</v>
       </c>
       <c r="F65">
-        <v>162.855</v>
+        <v>165.44</v>
       </c>
       <c r="G65">
         <v>25.2</v>
@@ -6617,28 +6617,28 @@
         <v>50.425</v>
       </c>
       <c r="M65">
-        <v>9.005881499999999</v>
+        <v>9.148832000000001</v>
       </c>
       <c r="N65">
-        <v>41.4191185</v>
+        <v>41.276168</v>
       </c>
       <c r="O65">
         <v>0</v>
       </c>
       <c r="P65">
-        <v>41.4191185</v>
+        <v>41.276168</v>
       </c>
       <c r="Q65">
-        <v>49.1191185</v>
+        <v>48.976168</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2228182638377307</v>
+        <v>0.2277354378332233</v>
       </c>
       <c r="T65">
-        <v>3.450415446118587</v>
+        <v>3.546260319621881</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.599118753672253</v>
+        <v>5.511632523146123</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1173767576199604</v>
+        <v>0.1174717576199604</v>
       </c>
       <c r="C66">
-        <v>94.76451486021597</v>
+        <v>92.02773832290356</v>
       </c>
       <c r="D66">
-        <v>235.004514860216</v>
+        <v>234.8527383229036</v>
       </c>
       <c r="E66">
-        <v>45.64</v>
+        <v>48.22500000000001</v>
       </c>
       <c r="F66">
-        <v>165.44</v>
+        <v>168.025</v>
       </c>
       <c r="G66">
         <v>25.2</v>
@@ -6699,28 +6699,28 @@
         <v>50.425</v>
       </c>
       <c r="M66">
-        <v>9.148832000000001</v>
+        <v>9.2917825</v>
       </c>
       <c r="N66">
-        <v>41.276168</v>
+        <v>41.1332175</v>
       </c>
       <c r="O66">
         <v>0</v>
       </c>
       <c r="P66">
-        <v>41.276168</v>
+        <v>41.1332175</v>
       </c>
       <c r="Q66">
-        <v>48.976168</v>
+        <v>48.8332175</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2277354378332233</v>
+        <v>0.2329335931998868</v>
       </c>
       <c r="T66">
-        <v>3.546260319621881</v>
+        <v>3.64758204303965</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.511632523146123</v>
+        <v>5.426838176636184</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1174717576199604</v>
+        <v>0.1175667576199604</v>
       </c>
       <c r="C67">
-        <v>92.02773832290356</v>
+        <v>89.29115770735149</v>
       </c>
       <c r="D67">
-        <v>234.8527383229036</v>
+        <v>234.7011577073515</v>
       </c>
       <c r="E67">
-        <v>48.22500000000001</v>
+        <v>50.81000000000002</v>
       </c>
       <c r="F67">
-        <v>168.025</v>
+        <v>170.61</v>
       </c>
       <c r="G67">
         <v>25.2</v>
@@ -6781,28 +6781,28 @@
         <v>50.425</v>
       </c>
       <c r="M67">
-        <v>9.2917825</v>
+        <v>9.434733000000001</v>
       </c>
       <c r="N67">
-        <v>41.1332175</v>
+        <v>40.990267</v>
       </c>
       <c r="O67">
         <v>0</v>
       </c>
       <c r="P67">
-        <v>41.1332175</v>
+        <v>40.990267</v>
       </c>
       <c r="Q67">
-        <v>48.8332175</v>
+        <v>48.690267</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2329335931998868</v>
+        <v>0.2384375224116482</v>
       </c>
       <c r="T67">
-        <v>3.64758204303965</v>
+        <v>3.754863867834934</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.426838176636184</v>
+        <v>5.344613355778058</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1175667576199604</v>
+        <v>0.1176617576199604</v>
       </c>
       <c r="C68">
-        <v>89.29115770735149</v>
+        <v>86.55477263444405</v>
       </c>
       <c r="D68">
-        <v>234.7011577073515</v>
+        <v>234.5497726344441</v>
       </c>
       <c r="E68">
-        <v>50.81000000000002</v>
+        <v>53.39500000000002</v>
       </c>
       <c r="F68">
-        <v>170.61</v>
+        <v>173.195</v>
       </c>
       <c r="G68">
         <v>25.2</v>
@@ -6863,28 +6863,28 @@
         <v>50.425</v>
       </c>
       <c r="M68">
-        <v>9.434733000000001</v>
+        <v>9.577683500000001</v>
       </c>
       <c r="N68">
-        <v>40.990267</v>
+        <v>40.8473165</v>
       </c>
       <c r="O68">
         <v>0</v>
       </c>
       <c r="P68">
-        <v>40.990267</v>
+        <v>40.8473165</v>
       </c>
       <c r="Q68">
-        <v>48.690267</v>
+        <v>48.5473165</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2384375224116482</v>
+        <v>0.2442750230907891</v>
       </c>
       <c r="T68">
-        <v>3.754863867834934</v>
+        <v>3.868647621405689</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.344613355778058</v>
+        <v>5.264843007184357</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1176617576199604</v>
+        <v>0.1177567576199604</v>
       </c>
       <c r="C69">
-        <v>86.55477263444405</v>
+        <v>83.81858272604299</v>
       </c>
       <c r="D69">
-        <v>234.5497726344441</v>
+        <v>234.398582726043</v>
       </c>
       <c r="E69">
-        <v>53.39500000000002</v>
+        <v>55.98</v>
       </c>
       <c r="F69">
-        <v>173.195</v>
+        <v>175.78</v>
       </c>
       <c r="G69">
         <v>25.2</v>
@@ -6945,28 +6945,28 @@
         <v>50.425</v>
       </c>
       <c r="M69">
-        <v>9.577683500000001</v>
+        <v>9.720634</v>
       </c>
       <c r="N69">
-        <v>40.8473165</v>
+        <v>40.70436599999999</v>
       </c>
       <c r="O69">
         <v>0</v>
       </c>
       <c r="P69">
-        <v>40.8473165</v>
+        <v>40.70436599999999</v>
       </c>
       <c r="Q69">
-        <v>48.5473165</v>
+        <v>48.404366</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2442750230907891</v>
+        <v>0.2504773675623762</v>
       </c>
       <c r="T69">
-        <v>3.868647621405689</v>
+        <v>3.989542859574617</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.264843007184357</v>
+        <v>5.187418845313998</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1177567576199604</v>
+        <v>0.1178517576199604</v>
       </c>
       <c r="C70">
-        <v>83.81858272604299</v>
+        <v>81.08258760498461</v>
       </c>
       <c r="D70">
-        <v>234.398582726043</v>
+        <v>234.2475876049846</v>
       </c>
       <c r="E70">
-        <v>55.98</v>
+        <v>58.56500000000001</v>
       </c>
       <c r="F70">
-        <v>175.78</v>
+        <v>178.365</v>
       </c>
       <c r="G70">
         <v>25.2</v>
@@ -7027,28 +7027,28 @@
         <v>50.425</v>
       </c>
       <c r="M70">
-        <v>9.720634</v>
+        <v>9.8635845</v>
       </c>
       <c r="N70">
-        <v>40.70436599999999</v>
+        <v>40.5614155</v>
       </c>
       <c r="O70">
         <v>0</v>
       </c>
       <c r="P70">
-        <v>40.70436599999999</v>
+        <v>40.5614155</v>
       </c>
       <c r="Q70">
-        <v>48.404366</v>
+        <v>48.2614155</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2504773675623762</v>
+        <v>0.2570798632901948</v>
       </c>
       <c r="T70">
-        <v>3.989542859574617</v>
+        <v>4.118237790528637</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.187418845313998</v>
+        <v>5.112238862048578</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1178517576199604</v>
+        <v>0.1179467576199604</v>
       </c>
       <c r="C71">
-        <v>81.08258760498461</v>
+        <v>78.34678689507618</v>
       </c>
       <c r="D71">
-        <v>234.2475876049846</v>
+        <v>234.0967868950762</v>
       </c>
       <c r="E71">
-        <v>58.56500000000001</v>
+        <v>61.15000000000002</v>
       </c>
       <c r="F71">
-        <v>178.365</v>
+        <v>180.95</v>
       </c>
       <c r="G71">
         <v>25.2</v>
@@ -7109,28 +7109,28 @@
         <v>50.425</v>
       </c>
       <c r="M71">
-        <v>9.8635845</v>
+        <v>10.006535</v>
       </c>
       <c r="N71">
-        <v>40.5614155</v>
+        <v>40.418465</v>
       </c>
       <c r="O71">
         <v>0</v>
       </c>
       <c r="P71">
-        <v>40.5614155</v>
+        <v>40.418465</v>
       </c>
       <c r="Q71">
-        <v>48.2614155</v>
+        <v>48.118465</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2570798632901948</v>
+        <v>0.264122525399868</v>
       </c>
       <c r="T71">
-        <v>4.118237790528637</v>
+        <v>4.255512383546258</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.112238862048578</v>
+        <v>5.039206878305027</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1179467576199604</v>
+        <v>0.1180417576199604</v>
       </c>
       <c r="C72">
-        <v>78.34678689507618</v>
+        <v>75.61118022109332</v>
       </c>
       <c r="D72">
-        <v>234.0967868950762</v>
+        <v>233.9461802210933</v>
       </c>
       <c r="E72">
-        <v>61.15000000000002</v>
+        <v>63.73500000000003</v>
       </c>
       <c r="F72">
-        <v>180.95</v>
+        <v>183.535</v>
       </c>
       <c r="G72">
         <v>25.2</v>
@@ -7191,28 +7191,28 @@
         <v>50.425</v>
       </c>
       <c r="M72">
-        <v>10.006535</v>
+        <v>10.1494855</v>
       </c>
       <c r="N72">
-        <v>40.418465</v>
+        <v>40.27551449999999</v>
       </c>
       <c r="O72">
         <v>0</v>
       </c>
       <c r="P72">
-        <v>40.418465</v>
+        <v>40.27551449999999</v>
       </c>
       <c r="Q72">
-        <v>48.118465</v>
+        <v>47.9755145</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.264122525399868</v>
+        <v>0.271650888344691</v>
       </c>
       <c r="T72">
-        <v>4.255512383546258</v>
+        <v>4.40225418987544</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.039206878305027</v>
+        <v>4.968232133540166</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1180417576199604</v>
+        <v>0.1181367576199604</v>
       </c>
       <c r="C73">
-        <v>75.61118022109335</v>
+        <v>72.87576720877649</v>
       </c>
       <c r="D73">
-        <v>233.9461802210933</v>
+        <v>233.7957672087765</v>
       </c>
       <c r="E73">
-        <v>63.735</v>
+        <v>66.32000000000001</v>
       </c>
       <c r="F73">
-        <v>183.535</v>
+        <v>186.12</v>
       </c>
       <c r="G73">
         <v>25.2</v>
@@ -7273,28 +7273,28 @@
         <v>50.425</v>
       </c>
       <c r="M73">
-        <v>10.1494855</v>
+        <v>10.292436</v>
       </c>
       <c r="N73">
-        <v>40.2755145</v>
+        <v>40.132564</v>
       </c>
       <c r="O73">
         <v>0</v>
       </c>
       <c r="P73">
-        <v>40.2755145</v>
+        <v>40.132564</v>
       </c>
       <c r="Q73">
-        <v>47.9755145</v>
+        <v>47.832564</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2716508883446909</v>
+        <v>0.2797169914998585</v>
       </c>
       <c r="T73">
-        <v>4.402254189875438</v>
+        <v>4.559477553799561</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.968232133540168</v>
+        <v>4.89922890946322</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1181367576199604</v>
+        <v>0.1182317576199604</v>
       </c>
       <c r="C74">
-        <v>72.87576720877649</v>
+        <v>70.14054748482801</v>
       </c>
       <c r="D74">
-        <v>233.7957672087765</v>
+        <v>233.645547484828</v>
       </c>
       <c r="E74">
-        <v>66.32000000000001</v>
+        <v>68.90499999999999</v>
       </c>
       <c r="F74">
-        <v>186.12</v>
+        <v>188.705</v>
       </c>
       <c r="G74">
         <v>25.2</v>
@@ -7355,28 +7355,28 @@
         <v>50.425</v>
       </c>
       <c r="M74">
-        <v>10.292436</v>
+        <v>10.4353865</v>
       </c>
       <c r="N74">
-        <v>40.132564</v>
+        <v>39.9896135</v>
       </c>
       <c r="O74">
         <v>0</v>
       </c>
       <c r="P74">
-        <v>40.132564</v>
+        <v>39.9896135</v>
       </c>
       <c r="Q74">
-        <v>47.832564</v>
+        <v>47.6896135</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2797169914998585</v>
+        <v>0.288380583777631</v>
       </c>
       <c r="T74">
-        <v>4.559477553799561</v>
+        <v>4.728347092829175</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.89922890946322</v>
+        <v>4.832116184676053</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1182317576199604</v>
+        <v>0.1183267576199604</v>
       </c>
       <c r="C75">
-        <v>70.14054748482801</v>
+        <v>67.40552067690905</v>
       </c>
       <c r="D75">
-        <v>233.645547484828</v>
+        <v>233.4955206769091</v>
       </c>
       <c r="E75">
-        <v>68.90499999999999</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="F75">
-        <v>188.705</v>
+        <v>191.29</v>
       </c>
       <c r="G75">
         <v>25.2</v>
@@ -7437,28 +7437,28 @@
         <v>50.425</v>
       </c>
       <c r="M75">
-        <v>10.4353865</v>
+        <v>10.578337</v>
       </c>
       <c r="N75">
-        <v>39.9896135</v>
+        <v>39.846663</v>
       </c>
       <c r="O75">
         <v>0</v>
       </c>
       <c r="P75">
-        <v>39.9896135</v>
+        <v>39.846663</v>
       </c>
       <c r="Q75">
-        <v>47.6896135</v>
+        <v>47.546663</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.288380583777631</v>
+        <v>0.2977106062306168</v>
       </c>
       <c r="T75">
-        <v>4.728347092829175</v>
+        <v>4.910206596399528</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.832116184676053</v>
+        <v>4.766817317315567</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1183267576199604</v>
+        <v>0.1184217576199604</v>
       </c>
       <c r="C76">
-        <v>67.40552067690905</v>
+        <v>64.67068641363653</v>
       </c>
       <c r="D76">
-        <v>233.4955206769091</v>
+        <v>233.3456864136365</v>
       </c>
       <c r="E76">
-        <v>71.48999999999999</v>
+        <v>74.075</v>
       </c>
       <c r="F76">
-        <v>191.29</v>
+        <v>193.875</v>
       </c>
       <c r="G76">
         <v>25.2</v>
@@ -7519,28 +7519,28 @@
         <v>50.425</v>
       </c>
       <c r="M76">
-        <v>10.578337</v>
+        <v>10.7212875</v>
       </c>
       <c r="N76">
-        <v>39.846663</v>
+        <v>39.70371249999999</v>
       </c>
       <c r="O76">
         <v>0</v>
       </c>
       <c r="P76">
-        <v>39.846663</v>
+        <v>39.70371249999999</v>
       </c>
       <c r="Q76">
-        <v>47.546663</v>
+        <v>47.4037125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2977106062306168</v>
+        <v>0.3077870304798415</v>
       </c>
       <c r="T76">
-        <v>4.910206596399528</v>
+        <v>5.106614860255509</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.766817317315567</v>
+        <v>4.703259753084692</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1184217576199604</v>
+        <v>0.1185167576199604</v>
       </c>
       <c r="C77">
-        <v>64.67068641363653</v>
+        <v>61.93604432457997</v>
       </c>
       <c r="D77">
-        <v>233.3456864136365</v>
+        <v>233.19604432458</v>
       </c>
       <c r="E77">
-        <v>74.075</v>
+        <v>76.66000000000001</v>
       </c>
       <c r="F77">
-        <v>193.875</v>
+        <v>196.46</v>
       </c>
       <c r="G77">
         <v>25.2</v>
@@ -7601,28 +7601,28 @@
         <v>50.425</v>
       </c>
       <c r="M77">
-        <v>10.7212875</v>
+        <v>10.864238</v>
       </c>
       <c r="N77">
-        <v>39.70371249999999</v>
+        <v>39.560762</v>
       </c>
       <c r="O77">
         <v>0</v>
       </c>
       <c r="P77">
-        <v>39.70371249999999</v>
+        <v>39.560762</v>
       </c>
       <c r="Q77">
-        <v>47.4037125</v>
+        <v>47.260762</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3077870304798415</v>
+        <v>0.318703156749835</v>
       </c>
       <c r="T77">
-        <v>5.106614860255509</v>
+        <v>5.319390479432823</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.703259753084692</v>
+        <v>4.641374756333578</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1185167576199604</v>
+        <v>0.1186117576199604</v>
       </c>
       <c r="C78">
-        <v>61.93604432457997</v>
+        <v>59.20159404025856</v>
       </c>
       <c r="D78">
-        <v>233.19604432458</v>
+        <v>233.0465940402586</v>
       </c>
       <c r="E78">
-        <v>76.66000000000001</v>
+        <v>79.24500000000002</v>
       </c>
       <c r="F78">
-        <v>196.46</v>
+        <v>199.045</v>
       </c>
       <c r="G78">
         <v>25.2</v>
@@ -7683,28 +7683,28 @@
         <v>50.425</v>
       </c>
       <c r="M78">
-        <v>10.864238</v>
+        <v>11.0071885</v>
       </c>
       <c r="N78">
-        <v>39.560762</v>
+        <v>39.4178115</v>
       </c>
       <c r="O78">
         <v>0</v>
       </c>
       <c r="P78">
-        <v>39.560762</v>
+        <v>39.4178115</v>
       </c>
       <c r="Q78">
-        <v>47.260762</v>
+        <v>47.1178115</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.318703156749835</v>
+        <v>0.3305685113911321</v>
       </c>
       <c r="T78">
-        <v>5.319390479432823</v>
+        <v>5.550668326364684</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.641374756333578</v>
+        <v>4.581097162095479</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1186117576199604</v>
+        <v>0.1187067576199604</v>
       </c>
       <c r="C79">
-        <v>59.20159404025856</v>
+        <v>56.46733519213802</v>
       </c>
       <c r="D79">
-        <v>233.0465940402586</v>
+        <v>232.897335192138</v>
       </c>
       <c r="E79">
-        <v>79.24500000000002</v>
+        <v>81.83</v>
       </c>
       <c r="F79">
-        <v>199.045</v>
+        <v>201.63</v>
       </c>
       <c r="G79">
         <v>25.2</v>
@@ -7765,28 +7765,28 @@
         <v>50.425</v>
       </c>
       <c r="M79">
-        <v>11.0071885</v>
+        <v>11.150139</v>
       </c>
       <c r="N79">
-        <v>39.4178115</v>
+        <v>39.274861</v>
       </c>
       <c r="O79">
         <v>0</v>
       </c>
       <c r="P79">
-        <v>39.4178115</v>
+        <v>39.274861</v>
       </c>
       <c r="Q79">
-        <v>47.1178115</v>
+        <v>46.974861</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3305685113911321</v>
+        <v>0.3435125346361835</v>
       </c>
       <c r="T79">
-        <v>5.550668326364684</v>
+        <v>5.802971432108533</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.581097162095479</v>
+        <v>4.52236514719682</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1187067576199604</v>
+        <v>0.1207767576199604</v>
       </c>
       <c r="C80">
-        <v>56.46733519213802</v>
+        <v>50.67688001648881</v>
       </c>
       <c r="D80">
-        <v>232.897335192138</v>
+        <v>229.6918800164888</v>
       </c>
       <c r="E80">
-        <v>81.83</v>
+        <v>84.41500000000001</v>
       </c>
       <c r="F80">
-        <v>201.63</v>
+        <v>204.215</v>
       </c>
       <c r="G80">
         <v>25.2</v>
@@ -7847,45 +7847,45 @@
         <v>50.425</v>
       </c>
       <c r="M80">
-        <v>11.150139</v>
+        <v>11.803627</v>
       </c>
       <c r="N80">
-        <v>39.274861</v>
+        <v>38.621373</v>
       </c>
       <c r="O80">
         <v>0</v>
       </c>
       <c r="P80">
-        <v>39.274861</v>
+        <v>38.621373</v>
       </c>
       <c r="Q80">
-        <v>46.974861</v>
+        <v>46.321373</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3435125346361835</v>
+        <v>0.3576893219998114</v>
       </c>
       <c r="T80">
-        <v>5.802971432108533</v>
+        <v>6.079303405066083</v>
       </c>
       <c r="U80">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V80">
         <v>0</v>
       </c>
       <c r="W80">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y80">
-        <v>4.52236514719682</v>
+        <v>4.271991990258587</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1207767576199604</v>
+        <v>0.1208967576199604</v>
       </c>
       <c r="C81">
-        <v>50.67688001648881</v>
+        <v>47.90876019499072</v>
       </c>
       <c r="D81">
-        <v>229.6918800164888</v>
+        <v>229.5087601949907</v>
       </c>
       <c r="E81">
-        <v>84.41500000000001</v>
+        <v>87.00000000000001</v>
       </c>
       <c r="F81">
-        <v>204.215</v>
+        <v>206.8</v>
       </c>
       <c r="G81">
         <v>25.2</v>
@@ -7929,28 +7929,28 @@
         <v>50.425</v>
       </c>
       <c r="M81">
-        <v>11.803627</v>
+        <v>11.95304</v>
       </c>
       <c r="N81">
-        <v>38.621373</v>
+        <v>38.47196</v>
       </c>
       <c r="O81">
         <v>0</v>
       </c>
       <c r="P81">
-        <v>38.621373</v>
+        <v>38.47196</v>
       </c>
       <c r="Q81">
-        <v>46.321373</v>
+        <v>46.17196</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3576893219998114</v>
+        <v>0.3732837880998019</v>
       </c>
       <c r="T81">
-        <v>6.079303405066083</v>
+        <v>6.383268575319388</v>
       </c>
       <c r="U81">
         <v>0.0578</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.271991990258587</v>
+        <v>4.218592090380355</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1208967576199604</v>
+        <v>0.1210167576199604</v>
       </c>
       <c r="C82">
-        <v>47.90876019499072</v>
+        <v>45.14093212221744</v>
       </c>
       <c r="D82">
-        <v>229.5087601949907</v>
+        <v>229.3259321222175</v>
       </c>
       <c r="E82">
-        <v>87.00000000000001</v>
+        <v>89.58500000000002</v>
       </c>
       <c r="F82">
-        <v>206.8</v>
+        <v>209.385</v>
       </c>
       <c r="G82">
         <v>25.2</v>
@@ -8011,28 +8011,28 @@
         <v>50.425</v>
       </c>
       <c r="M82">
-        <v>11.95304</v>
+        <v>12.102453</v>
       </c>
       <c r="N82">
-        <v>38.47196</v>
+        <v>38.32254699999999</v>
       </c>
       <c r="O82">
         <v>0</v>
       </c>
       <c r="P82">
-        <v>38.47196</v>
+        <v>38.32254699999999</v>
       </c>
       <c r="Q82">
-        <v>46.17196</v>
+        <v>46.022547</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3732837880998019</v>
+        <v>0.3905197769471599</v>
       </c>
       <c r="T82">
-        <v>6.383268575319388</v>
+        <v>6.719230079283566</v>
       </c>
       <c r="U82">
         <v>0.0578</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.218592090380355</v>
+        <v>4.166510706548498</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1210167576199604</v>
+        <v>0.1211367576199604</v>
       </c>
       <c r="C83">
-        <v>45.14093212221744</v>
+        <v>42.37339510149732</v>
       </c>
       <c r="D83">
-        <v>229.3259321222175</v>
+        <v>229.1433951014974</v>
       </c>
       <c r="E83">
-        <v>89.58500000000002</v>
+        <v>92.17000000000003</v>
       </c>
       <c r="F83">
-        <v>209.385</v>
+        <v>211.97</v>
       </c>
       <c r="G83">
         <v>25.2</v>
@@ -8093,28 +8093,28 @@
         <v>50.425</v>
       </c>
       <c r="M83">
-        <v>12.102453</v>
+        <v>12.251866</v>
       </c>
       <c r="N83">
-        <v>38.32254699999999</v>
+        <v>38.17313399999999</v>
       </c>
       <c r="O83">
         <v>0</v>
       </c>
       <c r="P83">
-        <v>38.32254699999999</v>
+        <v>38.17313399999999</v>
       </c>
       <c r="Q83">
-        <v>46.022547</v>
+        <v>45.87313399999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3905197769471599</v>
+        <v>0.4096708756664467</v>
       </c>
       <c r="T83">
-        <v>6.719230079283566</v>
+        <v>7.092520639243765</v>
       </c>
       <c r="U83">
         <v>0.0578</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.166510706548498</v>
+        <v>4.115699600371077</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1211367576199604</v>
+        <v>0.1212567576199604</v>
       </c>
       <c r="C84">
-        <v>42.37339510149732</v>
+        <v>39.60614843837553</v>
       </c>
       <c r="D84">
-        <v>229.1433951014974</v>
+        <v>228.9611484383755</v>
       </c>
       <c r="E84">
-        <v>92.17000000000003</v>
+        <v>94.75500000000001</v>
       </c>
       <c r="F84">
-        <v>211.97</v>
+        <v>214.555</v>
       </c>
       <c r="G84">
         <v>25.2</v>
@@ -8175,28 +8175,28 @@
         <v>50.425</v>
       </c>
       <c r="M84">
-        <v>12.251866</v>
+        <v>12.401279</v>
       </c>
       <c r="N84">
-        <v>38.17313399999999</v>
+        <v>38.02372099999999</v>
       </c>
       <c r="O84">
         <v>0</v>
       </c>
       <c r="P84">
-        <v>38.17313399999999</v>
+        <v>38.02372099999999</v>
       </c>
       <c r="Q84">
-        <v>45.87313399999999</v>
+        <v>45.723721</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4096708756664467</v>
+        <v>0.4310750448232964</v>
       </c>
       <c r="T84">
-        <v>7.092520639243765</v>
+        <v>7.509727735669869</v>
       </c>
       <c r="U84">
         <v>0.0578</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.115699600371077</v>
+        <v>4.066112858197933</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1212567576199604</v>
+        <v>0.1213767576199604</v>
       </c>
       <c r="C85">
-        <v>39.60614843837553</v>
+        <v>36.83919144060431</v>
       </c>
       <c r="D85">
-        <v>228.9611484383755</v>
+        <v>228.7791914406043</v>
       </c>
       <c r="E85">
-        <v>94.75500000000001</v>
+        <v>97.34000000000002</v>
       </c>
       <c r="F85">
-        <v>214.555</v>
+        <v>217.14</v>
       </c>
       <c r="G85">
         <v>25.2</v>
@@ -8257,28 +8257,28 @@
         <v>50.425</v>
       </c>
       <c r="M85">
-        <v>12.401279</v>
+        <v>12.550692</v>
       </c>
       <c r="N85">
-        <v>38.02372099999999</v>
+        <v>37.874308</v>
       </c>
       <c r="O85">
         <v>0</v>
       </c>
       <c r="P85">
-        <v>38.02372099999999</v>
+        <v>37.874308</v>
       </c>
       <c r="Q85">
-        <v>45.723721</v>
+        <v>45.574308</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4310750448232964</v>
+        <v>0.4551547351247526</v>
       </c>
       <c r="T85">
-        <v>7.509727735669869</v>
+        <v>7.979085719149237</v>
       </c>
       <c r="U85">
         <v>0.0578</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.066112858197933</v>
+        <v>4.017706752743194</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1213767576199604</v>
+        <v>0.1244717576199604</v>
       </c>
       <c r="C86">
-        <v>36.83919144060434</v>
+        <v>29.65913085075846</v>
       </c>
       <c r="D86">
-        <v>228.7791914406043</v>
+        <v>224.1841308507585</v>
       </c>
       <c r="E86">
-        <v>97.33999999999999</v>
+        <v>99.925</v>
       </c>
       <c r="F86">
-        <v>217.14</v>
+        <v>219.725</v>
       </c>
       <c r="G86">
         <v>25.2</v>
@@ -8339,45 +8339,45 @@
         <v>50.425</v>
       </c>
       <c r="M86">
-        <v>12.550692</v>
+        <v>13.4691425</v>
       </c>
       <c r="N86">
-        <v>37.874308</v>
+        <v>36.95585749999999</v>
       </c>
       <c r="O86">
         <v>0</v>
       </c>
       <c r="P86">
-        <v>37.874308</v>
+        <v>36.95585749999999</v>
       </c>
       <c r="Q86">
-        <v>45.574308</v>
+        <v>44.6558575</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4551547351247524</v>
+        <v>0.4824450507997358</v>
       </c>
       <c r="T86">
-        <v>7.979085719149232</v>
+        <v>8.511024767092515</v>
       </c>
       <c r="U86">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V86">
         <v>0</v>
       </c>
       <c r="W86">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y86">
-        <v>4.017706752743195</v>
+        <v>3.743742409733953</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1244717576199604</v>
+        <v>0.1246267576199604</v>
       </c>
       <c r="C87">
-        <v>29.65913085075846</v>
+        <v>26.84885532835295</v>
       </c>
       <c r="D87">
-        <v>224.1841308507585</v>
+        <v>223.958855328353</v>
       </c>
       <c r="E87">
-        <v>99.925</v>
+        <v>102.51</v>
       </c>
       <c r="F87">
-        <v>219.725</v>
+        <v>222.31</v>
       </c>
       <c r="G87">
         <v>25.2</v>
@@ -8421,28 +8421,28 @@
         <v>50.425</v>
       </c>
       <c r="M87">
-        <v>13.4691425</v>
+        <v>13.627603</v>
       </c>
       <c r="N87">
-        <v>36.95585749999999</v>
+        <v>36.797397</v>
       </c>
       <c r="O87">
         <v>0</v>
       </c>
       <c r="P87">
-        <v>36.95585749999999</v>
+        <v>36.797397</v>
       </c>
       <c r="Q87">
-        <v>44.6558575</v>
+        <v>44.497397</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4824450507997358</v>
+        <v>0.5136339829997169</v>
       </c>
       <c r="T87">
-        <v>8.511024767092515</v>
+        <v>9.118955107599122</v>
       </c>
       <c r="U87">
         <v>0.0613</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.743742409733953</v>
+        <v>3.700210521248674</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1246267576199604</v>
+        <v>0.1247817576199604</v>
       </c>
       <c r="C88">
-        <v>26.84885532835295</v>
+        <v>24.0390320959099</v>
       </c>
       <c r="D88">
-        <v>223.958855328353</v>
+        <v>223.7340320959099</v>
       </c>
       <c r="E88">
-        <v>102.51</v>
+        <v>105.095</v>
       </c>
       <c r="F88">
-        <v>222.31</v>
+        <v>224.895</v>
       </c>
       <c r="G88">
         <v>25.2</v>
@@ -8503,28 +8503,28 @@
         <v>50.425</v>
       </c>
       <c r="M88">
-        <v>13.627603</v>
+        <v>13.7860635</v>
       </c>
       <c r="N88">
-        <v>36.797397</v>
+        <v>36.6389365</v>
       </c>
       <c r="O88">
         <v>0</v>
       </c>
       <c r="P88">
-        <v>36.797397</v>
+        <v>36.6389365</v>
       </c>
       <c r="Q88">
-        <v>44.497397</v>
+        <v>44.3389365</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5136339829997169</v>
+        <v>0.5496212124612336</v>
       </c>
       <c r="T88">
-        <v>9.118955107599122</v>
+        <v>9.820413192799055</v>
       </c>
       <c r="U88">
         <v>0.0613</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.700210521248674</v>
+        <v>3.657679365832023</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1247817576199604</v>
+        <v>0.1249367576199604</v>
       </c>
       <c r="C89">
-        <v>24.0390320959099</v>
+        <v>21.22965979268858</v>
       </c>
       <c r="D89">
-        <v>223.7340320959099</v>
+        <v>223.5096597926886</v>
       </c>
       <c r="E89">
-        <v>105.095</v>
+        <v>107.68</v>
       </c>
       <c r="F89">
-        <v>224.895</v>
+        <v>227.48</v>
       </c>
       <c r="G89">
         <v>25.2</v>
@@ -8585,28 +8585,28 @@
         <v>50.425</v>
       </c>
       <c r="M89">
-        <v>13.7860635</v>
+        <v>13.944524</v>
       </c>
       <c r="N89">
-        <v>36.6389365</v>
+        <v>36.480476</v>
       </c>
       <c r="O89">
         <v>0</v>
       </c>
       <c r="P89">
-        <v>36.6389365</v>
+        <v>36.480476</v>
       </c>
       <c r="Q89">
-        <v>44.3389365</v>
+        <v>44.180476</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5496212124612336</v>
+        <v>0.5916063134996699</v>
       </c>
       <c r="T89">
-        <v>9.820413192799055</v>
+        <v>10.63878095886565</v>
       </c>
       <c r="U89">
         <v>0.0613</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.657679365832023</v>
+        <v>3.616114827583932</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1249367576199604</v>
+        <v>0.1250917576199604</v>
       </c>
       <c r="C90">
-        <v>21.22965979268858</v>
+        <v>18.42073706340122</v>
       </c>
       <c r="D90">
-        <v>223.5096597926886</v>
+        <v>223.2857370634012</v>
       </c>
       <c r="E90">
-        <v>107.68</v>
+        <v>110.265</v>
       </c>
       <c r="F90">
-        <v>227.48</v>
+        <v>230.065</v>
       </c>
       <c r="G90">
         <v>25.2</v>
@@ -8667,28 +8667,28 @@
         <v>50.425</v>
       </c>
       <c r="M90">
-        <v>13.944524</v>
+        <v>14.1029845</v>
       </c>
       <c r="N90">
-        <v>36.480476</v>
+        <v>36.3220155</v>
       </c>
       <c r="O90">
         <v>0</v>
       </c>
       <c r="P90">
-        <v>36.480476</v>
+        <v>36.3220155</v>
       </c>
       <c r="Q90">
-        <v>44.180476</v>
+        <v>44.0220155</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5916063134996699</v>
+        <v>0.641225069272367</v>
       </c>
       <c r="T90">
-        <v>10.63878095886565</v>
+        <v>11.60594286421707</v>
       </c>
       <c r="U90">
         <v>0.0613</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.616114827583932</v>
+        <v>3.575484323903213</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1250917576199604</v>
+        <v>0.1252467576199604</v>
       </c>
       <c r="C91">
-        <v>18.42073706340122</v>
+        <v>15.61226255818573</v>
       </c>
       <c r="D91">
-        <v>223.2857370634012</v>
+        <v>223.0622625581858</v>
       </c>
       <c r="E91">
-        <v>110.265</v>
+        <v>112.85</v>
       </c>
       <c r="F91">
-        <v>230.065</v>
+        <v>232.65</v>
       </c>
       <c r="G91">
         <v>25.2</v>
@@ -8749,28 +8749,28 @@
         <v>50.425</v>
       </c>
       <c r="M91">
-        <v>14.1029845</v>
+        <v>14.261445</v>
       </c>
       <c r="N91">
-        <v>36.3220155</v>
+        <v>36.163555</v>
       </c>
       <c r="O91">
         <v>0</v>
       </c>
       <c r="P91">
-        <v>36.3220155</v>
+        <v>36.163555</v>
       </c>
       <c r="Q91">
-        <v>44.0220155</v>
+        <v>43.863555</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.641225069272367</v>
+        <v>0.7007675761996038</v>
       </c>
       <c r="T91">
-        <v>11.60594286421707</v>
+        <v>12.76653715063878</v>
       </c>
       <c r="U91">
         <v>0.0613</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.575484323903213</v>
+        <v>3.535756720304289</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1252467576199604</v>
+        <v>0.1279497576199604</v>
       </c>
       <c r="C92">
-        <v>15.61226255818573</v>
+        <v>9.200840223748429</v>
       </c>
       <c r="D92">
-        <v>223.0622625581858</v>
+        <v>219.2358402237485</v>
       </c>
       <c r="E92">
-        <v>112.85</v>
+        <v>115.435</v>
       </c>
       <c r="F92">
-        <v>232.65</v>
+        <v>235.235</v>
       </c>
       <c r="G92">
         <v>25.2</v>
@@ -8831,45 +8831,45 @@
         <v>50.425</v>
       </c>
       <c r="M92">
-        <v>14.261445</v>
+        <v>15.0785635</v>
       </c>
       <c r="N92">
-        <v>36.163555</v>
+        <v>35.3464365</v>
       </c>
       <c r="O92">
         <v>0</v>
       </c>
       <c r="P92">
-        <v>36.163555</v>
+        <v>35.3464365</v>
       </c>
       <c r="Q92">
-        <v>43.863555</v>
+        <v>43.0464365</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7007675761996038</v>
+        <v>0.7735417513328933</v>
       </c>
       <c r="T92">
-        <v>12.76653715063878</v>
+        <v>14.18504127848753</v>
       </c>
       <c r="U92">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V92">
         <v>0</v>
       </c>
       <c r="W92">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y92">
-        <v>3.535756720304289</v>
+        <v>3.344151450501236</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1279497576199604</v>
+        <v>0.1281327576199604</v>
       </c>
       <c r="C93">
-        <v>9.200840223748429</v>
+        <v>6.361520928368748</v>
       </c>
       <c r="D93">
-        <v>219.2358402237485</v>
+        <v>218.9815209283688</v>
       </c>
       <c r="E93">
-        <v>115.435</v>
+        <v>118.02</v>
       </c>
       <c r="F93">
-        <v>235.235</v>
+        <v>237.82</v>
       </c>
       <c r="G93">
         <v>25.2</v>
@@ -8913,28 +8913,28 @@
         <v>50.425</v>
       </c>
       <c r="M93">
-        <v>15.0785635</v>
+        <v>15.244262</v>
       </c>
       <c r="N93">
-        <v>35.3464365</v>
+        <v>35.18073799999999</v>
       </c>
       <c r="O93">
         <v>0</v>
       </c>
       <c r="P93">
-        <v>35.3464365</v>
+        <v>35.18073799999999</v>
       </c>
       <c r="Q93">
-        <v>43.0464365</v>
+        <v>42.88073799999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7735417513328933</v>
+        <v>0.8645094702495051</v>
       </c>
       <c r="T93">
-        <v>14.18504127848753</v>
+        <v>15.95817143829847</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.344151450501236</v>
+        <v>3.307801978213178</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1281327576199604</v>
+        <v>0.1283157576199604</v>
       </c>
       <c r="C94">
-        <v>6.361520928368748</v>
+        <v>3.522790983364956</v>
       </c>
       <c r="D94">
-        <v>218.9815209283688</v>
+        <v>218.727790983365</v>
       </c>
       <c r="E94">
-        <v>118.02</v>
+        <v>120.605</v>
       </c>
       <c r="F94">
-        <v>237.82</v>
+        <v>240.405</v>
       </c>
       <c r="G94">
         <v>25.2</v>
@@ -8995,28 +8995,28 @@
         <v>50.425</v>
       </c>
       <c r="M94">
-        <v>15.244262</v>
+        <v>15.4099605</v>
       </c>
       <c r="N94">
-        <v>35.18073799999999</v>
+        <v>35.0150395</v>
       </c>
       <c r="O94">
         <v>0</v>
       </c>
       <c r="P94">
-        <v>35.18073799999999</v>
+        <v>35.0150395</v>
       </c>
       <c r="Q94">
-        <v>42.88073799999999</v>
+        <v>42.7150395</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8645094702495051</v>
+        <v>0.9814679659994345</v>
       </c>
       <c r="T94">
-        <v>15.95817143829847</v>
+        <v>18.23791021519826</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.307801978213178</v>
+        <v>3.272234215006586</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1283157576199604</v>
+        <v>0.1284987576199604</v>
       </c>
       <c r="C95">
-        <v>3.522790983364956</v>
+        <v>0.684648342498889</v>
       </c>
       <c r="D95">
-        <v>218.727790983365</v>
+        <v>218.4746483424989</v>
       </c>
       <c r="E95">
-        <v>120.605</v>
+        <v>123.19</v>
       </c>
       <c r="F95">
-        <v>240.405</v>
+        <v>242.99</v>
       </c>
       <c r="G95">
         <v>25.2</v>
@@ -9077,28 +9077,28 @@
         <v>50.425</v>
       </c>
       <c r="M95">
-        <v>15.4099605</v>
+        <v>15.575659</v>
       </c>
       <c r="N95">
-        <v>35.0150395</v>
+        <v>34.849341</v>
       </c>
       <c r="O95">
         <v>0</v>
       </c>
       <c r="P95">
-        <v>35.0150395</v>
+        <v>34.849341</v>
       </c>
       <c r="Q95">
-        <v>42.7150395</v>
+        <v>42.549341</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9814679659994345</v>
+        <v>1.137412626999341</v>
       </c>
       <c r="T95">
-        <v>18.23791021519826</v>
+        <v>21.27756191773131</v>
       </c>
       <c r="U95">
         <v>0.0641</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.272234215006586</v>
+        <v>3.237423212719281</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1284987576199604</v>
+        <v>0.1286817576199604</v>
       </c>
       <c r="C96">
-        <v>0.684648342498889</v>
+        <v>-2.152909031005635</v>
       </c>
       <c r="D96">
-        <v>218.4746483424989</v>
+        <v>218.2220909689944</v>
       </c>
       <c r="E96">
-        <v>123.19</v>
+        <v>125.775</v>
       </c>
       <c r="F96">
-        <v>242.99</v>
+        <v>245.575</v>
       </c>
       <c r="G96">
         <v>25.2</v>
@@ -9159,28 +9159,28 @@
         <v>50.425</v>
       </c>
       <c r="M96">
-        <v>15.575659</v>
+        <v>15.7413575</v>
       </c>
       <c r="N96">
-        <v>34.849341</v>
+        <v>34.68364249999999</v>
       </c>
       <c r="O96">
         <v>0</v>
       </c>
       <c r="P96">
-        <v>34.849341</v>
+        <v>34.68364249999999</v>
       </c>
       <c r="Q96">
-        <v>42.549341</v>
+        <v>42.38364249999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.137412626999341</v>
+        <v>1.355735152399209</v>
       </c>
       <c r="T96">
-        <v>21.27756191773131</v>
+        <v>25.53307430127758</v>
       </c>
       <c r="U96">
         <v>0.0641</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.237423212719281</v>
+        <v>3.203345073638026</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1286817576199604</v>
+        <v>0.1288647576199604</v>
       </c>
       <c r="C97">
-        <v>-2.152909031005635</v>
+        <v>-4.989883164517607</v>
       </c>
       <c r="D97">
-        <v>218.2220909689944</v>
+        <v>217.9701168354824</v>
       </c>
       <c r="E97">
-        <v>125.775</v>
+        <v>128.36</v>
       </c>
       <c r="F97">
-        <v>245.575</v>
+        <v>248.16</v>
       </c>
       <c r="G97">
         <v>25.2</v>
@@ -9241,28 +9241,28 @@
         <v>50.425</v>
       </c>
       <c r="M97">
-        <v>15.7413575</v>
+        <v>15.907056</v>
       </c>
       <c r="N97">
-        <v>34.68364249999999</v>
+        <v>34.51794399999999</v>
       </c>
       <c r="O97">
         <v>0</v>
       </c>
       <c r="P97">
-        <v>34.68364249999999</v>
+        <v>34.51794399999999</v>
       </c>
       <c r="Q97">
-        <v>42.38364249999999</v>
+        <v>42.217944</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.355735152399209</v>
+        <v>1.683218940499012</v>
       </c>
       <c r="T97">
-        <v>25.53307430127758</v>
+        <v>31.91634287659699</v>
       </c>
       <c r="U97">
         <v>0.0641</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.203345073638026</v>
+        <v>3.16997689578763</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1288647576199604</v>
+        <v>0.1290477576199604</v>
       </c>
       <c r="C98">
-        <v>-4.989883164517636</v>
+        <v>-7.826276076053233</v>
       </c>
       <c r="D98">
-        <v>217.9701168354824</v>
+        <v>217.7187239239468</v>
       </c>
       <c r="E98">
-        <v>128.36</v>
+        <v>130.945</v>
       </c>
       <c r="F98">
-        <v>248.16</v>
+        <v>250.745</v>
       </c>
       <c r="G98">
         <v>25.2</v>
@@ -9323,28 +9323,28 @@
         <v>50.425</v>
       </c>
       <c r="M98">
-        <v>15.907056</v>
+        <v>16.0727545</v>
       </c>
       <c r="N98">
-        <v>34.517944</v>
+        <v>34.3522455</v>
       </c>
       <c r="O98">
         <v>0</v>
       </c>
       <c r="P98">
-        <v>34.517944</v>
+        <v>34.3522455</v>
       </c>
       <c r="Q98">
-        <v>42.217944</v>
+        <v>42.0522455</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.683218940499008</v>
+        <v>2.229025253998678</v>
       </c>
       <c r="T98">
-        <v>31.9163428765969</v>
+        <v>42.55512383546255</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.16997689578763</v>
+        <v>3.137296721604252</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1290477576199604</v>
+        <v>0.1292307576199604</v>
       </c>
       <c r="C99">
-        <v>-7.826276076053233</v>
+        <v>-10.6620897743293</v>
       </c>
       <c r="D99">
-        <v>217.7187239239468</v>
+        <v>217.4679102256707</v>
       </c>
       <c r="E99">
-        <v>130.945</v>
+        <v>133.53</v>
       </c>
       <c r="F99">
-        <v>250.745</v>
+        <v>253.33</v>
       </c>
       <c r="G99">
         <v>25.2</v>
@@ -9405,28 +9405,28 @@
         <v>50.425</v>
       </c>
       <c r="M99">
-        <v>16.0727545</v>
+        <v>16.238453</v>
       </c>
       <c r="N99">
-        <v>34.3522455</v>
+        <v>34.186547</v>
       </c>
       <c r="O99">
         <v>0</v>
       </c>
       <c r="P99">
-        <v>34.3522455</v>
+        <v>34.186547</v>
       </c>
       <c r="Q99">
-        <v>42.0522455</v>
+        <v>41.886547</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.229025253998678</v>
+        <v>3.320637880998016</v>
       </c>
       <c r="T99">
-        <v>42.55512383546255</v>
+        <v>63.83268575319381</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.137296721604252</v>
+        <v>3.105283489751148</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1292307576199604</v>
+        <v>0.1294137576199604</v>
       </c>
       <c r="C100">
-        <v>-10.6620897743293</v>
+        <v>-13.49732625881742</v>
       </c>
       <c r="D100">
-        <v>217.4679102256707</v>
+        <v>217.2176737411826</v>
       </c>
       <c r="E100">
-        <v>133.53</v>
+        <v>136.115</v>
       </c>
       <c r="F100">
-        <v>253.33</v>
+        <v>255.915</v>
       </c>
       <c r="G100">
         <v>25.2</v>
@@ -9487,28 +9487,28 @@
         <v>50.425</v>
       </c>
       <c r="M100">
-        <v>16.238453</v>
+        <v>16.4041515</v>
       </c>
       <c r="N100">
-        <v>34.186547</v>
+        <v>34.0208485</v>
       </c>
       <c r="O100">
         <v>0</v>
       </c>
       <c r="P100">
-        <v>34.186547</v>
+        <v>34.0208485</v>
       </c>
       <c r="Q100">
-        <v>41.886547</v>
+        <v>41.7208485</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.320637880998016</v>
+        <v>6.595475761996032</v>
       </c>
       <c r="T100">
-        <v>63.83268575319381</v>
+        <v>127.6653715063876</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.105283489751148</v>
+        <v>3.073916989854672</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1294137576199604</v>
-      </c>
-      <c r="C101">
-        <v>-13.49732625881742</v>
-      </c>
-      <c r="D101">
-        <v>217.2176737411826</v>
-      </c>
-      <c r="E101">
-        <v>136.115</v>
-      </c>
-      <c r="F101">
-        <v>255.915</v>
-      </c>
-      <c r="G101">
-        <v>25.2</v>
-      </c>
-      <c r="H101">
-        <v>138.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>58.125</v>
-      </c>
-      <c r="K101">
-        <v>7.700000000000003</v>
-      </c>
-      <c r="L101">
-        <v>50.425</v>
-      </c>
-      <c r="M101">
-        <v>16.4041515</v>
-      </c>
-      <c r="N101">
-        <v>34.0208485</v>
-      </c>
-      <c r="O101">
-        <v>0</v>
-      </c>
-      <c r="P101">
-        <v>34.0208485</v>
-      </c>
-      <c r="Q101">
-        <v>41.7208485</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.595475761996032</v>
-      </c>
-      <c r="T101">
-        <v>127.6653715063876</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.0641</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.073916989854672</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
